--- a/research/traditional_assets/database/data/pakistan/pakistan_recreation.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_recreation.xlsx
@@ -588,43 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0567</v>
+        <v>0.111</v>
+      </c>
+      <c r="E2">
+        <v>0.532</v>
       </c>
       <c r="G2">
-        <v>0.09545454545454544</v>
+        <v>0.04785276073619632</v>
       </c>
       <c r="H2">
-        <v>0.09545454545454544</v>
+        <v>0.04785276073619632</v>
       </c>
       <c r="I2">
-        <v>0.004545454545454545</v>
+        <v>0.09079754601226994</v>
       </c>
       <c r="J2">
-        <v>0.002272727272727273</v>
+        <v>0.0861172601353488</v>
       </c>
       <c r="K2">
-        <v>-0.003</v>
+        <v>0.552</v>
       </c>
       <c r="L2">
-        <v>-0.002727272727272727</v>
+        <v>0.3386503067484663</v>
       </c>
       <c r="M2">
-        <v>0.043</v>
+        <v>0.0294</v>
       </c>
       <c r="N2">
-        <v>0.0180672268907563</v>
+        <v>0.01330316742081448</v>
       </c>
       <c r="O2">
-        <v>-14.33333333333333</v>
+        <v>0.05326086956521738</v>
       </c>
       <c r="P2">
-        <v>0.043</v>
+        <v>0.0294</v>
       </c>
       <c r="Q2">
-        <v>0.0180672268907563</v>
+        <v>0.01330316742081448</v>
       </c>
       <c r="R2">
-        <v>-14.33333333333333</v>
+        <v>0.05326086956521738</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.33</v>
+        <v>0.463</v>
       </c>
       <c r="V2">
-        <v>0.138655462184874</v>
+        <v>0.2095022624434389</v>
       </c>
       <c r="W2">
-        <v>-0.001442307692307692</v>
+        <v>0.2802030456852792</v>
       </c>
       <c r="X2">
-        <v>0.1219614705900466</v>
+        <v>0.225393102521382</v>
       </c>
       <c r="Y2">
-        <v>-0.1234037782823542</v>
+        <v>0.0548099431638972</v>
       </c>
       <c r="Z2">
-        <v>0.6962025316455697</v>
+        <v>0.9939024390243902</v>
       </c>
       <c r="AA2">
-        <v>0.001582278481012658</v>
+        <v>0.08559215489062107</v>
       </c>
       <c r="AB2">
-        <v>0.1219614705900466</v>
+        <v>0.225393102521382</v>
       </c>
       <c r="AC2">
-        <v>-0.1203791921090339</v>
+        <v>-0.139800947630761</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -669,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.33</v>
+        <v>-0.463</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -678,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.1609756097560976</v>
+        <v>-0.2650257584430453</v>
       </c>
       <c r="AK2">
-        <v>-0.201219512195122</v>
+        <v>-0.2973667308927425</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.019</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-5.593220338983051</v>
+        <v>-2.338383838383838</v>
       </c>
       <c r="AQ2">
-        <v>-0.2631578947368421</v>
+        <v>-16.44444444444445</v>
       </c>
     </row>
     <row r="3">
@@ -716,43 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0567</v>
+        <v>0.111</v>
+      </c>
+      <c r="E3">
+        <v>0.532</v>
       </c>
       <c r="G3">
-        <v>0.09545454545454544</v>
+        <v>0.04785276073619632</v>
       </c>
       <c r="H3">
-        <v>0.09545454545454544</v>
+        <v>0.04785276073619632</v>
       </c>
       <c r="I3">
-        <v>0.004545454545454545</v>
+        <v>0.09079754601226994</v>
       </c>
       <c r="J3">
-        <v>0.002272727272727273</v>
+        <v>0.0861172601353488</v>
       </c>
       <c r="K3">
-        <v>-0.003</v>
+        <v>0.552</v>
       </c>
       <c r="L3">
-        <v>-0.002727272727272727</v>
+        <v>0.3386503067484663</v>
       </c>
       <c r="M3">
-        <v>0.043</v>
+        <v>0.0294</v>
       </c>
       <c r="N3">
-        <v>0.0180672268907563</v>
+        <v>0.01330316742081448</v>
       </c>
       <c r="O3">
-        <v>-14.33333333333333</v>
+        <v>0.05326086956521738</v>
       </c>
       <c r="P3">
-        <v>0.043</v>
+        <v>0.0294</v>
       </c>
       <c r="Q3">
-        <v>0.0180672268907563</v>
+        <v>0.01330316742081448</v>
       </c>
       <c r="R3">
-        <v>-14.33333333333333</v>
+        <v>0.05326086956521738</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.33</v>
+        <v>0.463</v>
       </c>
       <c r="V3">
-        <v>0.138655462184874</v>
+        <v>0.2095022624434389</v>
       </c>
       <c r="W3">
-        <v>-0.001442307692307692</v>
+        <v>0.2802030456852792</v>
       </c>
       <c r="X3">
-        <v>0.1219614705900466</v>
+        <v>0.225393102521382</v>
       </c>
       <c r="Y3">
-        <v>-0.1234037782823542</v>
+        <v>0.0548099431638972</v>
       </c>
       <c r="Z3">
-        <v>0.6962025316455697</v>
+        <v>0.9939024390243902</v>
       </c>
       <c r="AA3">
-        <v>0.001582278481012658</v>
+        <v>0.08559215489062107</v>
       </c>
       <c r="AB3">
-        <v>0.1219614705900466</v>
+        <v>0.225393102521382</v>
       </c>
       <c r="AC3">
-        <v>-0.1203791921090339</v>
+        <v>-0.139800947630761</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -797,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.33</v>
+        <v>-0.463</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -806,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1609756097560976</v>
+        <v>-0.2650257584430453</v>
       </c>
       <c r="AK3">
-        <v>-0.201219512195122</v>
+        <v>-0.2973667308927425</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.019</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-5.593220338983051</v>
+        <v>-2.338383838383838</v>
       </c>
       <c r="AQ3">
-        <v>-0.2631578947368421</v>
+        <v>-16.44444444444445</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_recreation.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_recreation.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.111</v>
+        <v>0.233</v>
       </c>
       <c r="E2">
-        <v>0.532</v>
+        <v>0.457</v>
       </c>
       <c r="G2">
-        <v>0.04785276073619632</v>
+        <v>0.2103448275862069</v>
       </c>
       <c r="H2">
-        <v>0.04785276073619632</v>
+        <v>0.2103448275862069</v>
       </c>
       <c r="I2">
-        <v>0.09079754601226994</v>
+        <v>0.1961206896551724</v>
       </c>
       <c r="J2">
-        <v>0.0861172601353488</v>
+        <v>0.1836095422116528</v>
       </c>
       <c r="K2">
-        <v>0.552</v>
+        <v>0.543</v>
       </c>
       <c r="L2">
-        <v>0.3386503067484663</v>
+        <v>0.2340517241379311</v>
       </c>
       <c r="M2">
-        <v>0.0294</v>
+        <v>0.025</v>
       </c>
       <c r="N2">
-        <v>0.01330316742081448</v>
+        <v>0.01748251748251748</v>
       </c>
       <c r="O2">
-        <v>0.05326086956521738</v>
+        <v>0.04604051565377532</v>
       </c>
       <c r="P2">
-        <v>0.0294</v>
+        <v>0.025</v>
       </c>
       <c r="Q2">
-        <v>0.01330316742081448</v>
+        <v>0.01748251748251748</v>
       </c>
       <c r="R2">
-        <v>0.05326086956521738</v>
+        <v>0.04604051565377532</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.463</v>
+        <v>0.235</v>
       </c>
       <c r="V2">
-        <v>0.2095022624434389</v>
+        <v>0.1643356643356643</v>
       </c>
       <c r="W2">
-        <v>0.2802030456852792</v>
+        <v>0.2688118811881188</v>
       </c>
       <c r="X2">
-        <v>0.225393102521382</v>
+        <v>0.211264995619857</v>
       </c>
       <c r="Y2">
-        <v>0.0548099431638972</v>
+        <v>0.05754688556826185</v>
       </c>
       <c r="Z2">
-        <v>0.9939024390243902</v>
+        <v>1.490044958253051</v>
       </c>
       <c r="AA2">
-        <v>0.08559215489062107</v>
+        <v>0.273586472659624</v>
       </c>
       <c r="AB2">
-        <v>0.225393102521382</v>
+        <v>0.211264995619857</v>
       </c>
       <c r="AC2">
-        <v>-0.139800947630761</v>
+        <v>0.06232147703976701</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.463</v>
+        <v>-0.235</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.2650257584430453</v>
+        <v>-0.196652719665272</v>
       </c>
       <c r="AK2">
-        <v>-0.2973667308927425</v>
+        <v>-0.1246684350132626</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.008999999999999999</v>
+        <v>-0.034</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-2.338383838383838</v>
+        <v>-0.4681274900398406</v>
       </c>
       <c r="AQ2">
-        <v>-16.44444444444445</v>
+        <v>-13.38235294117647</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.111</v>
+        <v>0.233</v>
       </c>
       <c r="E3">
-        <v>0.532</v>
+        <v>0.457</v>
       </c>
       <c r="G3">
-        <v>0.04785276073619632</v>
+        <v>0.2103448275862069</v>
       </c>
       <c r="H3">
-        <v>0.04785276073619632</v>
+        <v>0.2103448275862069</v>
       </c>
       <c r="I3">
-        <v>0.09079754601226994</v>
+        <v>0.1961206896551724</v>
       </c>
       <c r="J3">
-        <v>0.0861172601353488</v>
+        <v>0.1836095422116528</v>
       </c>
       <c r="K3">
-        <v>0.552</v>
+        <v>0.543</v>
       </c>
       <c r="L3">
-        <v>0.3386503067484663</v>
+        <v>0.2340517241379311</v>
       </c>
       <c r="M3">
-        <v>0.0294</v>
+        <v>0.025</v>
       </c>
       <c r="N3">
-        <v>0.01330316742081448</v>
+        <v>0.01748251748251748</v>
       </c>
       <c r="O3">
-        <v>0.05326086956521738</v>
+        <v>0.04604051565377532</v>
       </c>
       <c r="P3">
-        <v>0.0294</v>
+        <v>0.025</v>
       </c>
       <c r="Q3">
-        <v>0.01330316742081448</v>
+        <v>0.01748251748251748</v>
       </c>
       <c r="R3">
-        <v>0.05326086956521738</v>
+        <v>0.04604051565377532</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.463</v>
+        <v>0.235</v>
       </c>
       <c r="V3">
-        <v>0.2095022624434389</v>
+        <v>0.1643356643356643</v>
       </c>
       <c r="W3">
-        <v>0.2802030456852792</v>
+        <v>0.2688118811881188</v>
       </c>
       <c r="X3">
-        <v>0.225393102521382</v>
+        <v>0.211264995619857</v>
       </c>
       <c r="Y3">
-        <v>0.0548099431638972</v>
+        <v>0.05754688556826185</v>
       </c>
       <c r="Z3">
-        <v>0.9939024390243902</v>
+        <v>1.490044958253051</v>
       </c>
       <c r="AA3">
-        <v>0.08559215489062107</v>
+        <v>0.273586472659624</v>
       </c>
       <c r="AB3">
-        <v>0.225393102521382</v>
+        <v>0.211264995619857</v>
       </c>
       <c r="AC3">
-        <v>-0.139800947630761</v>
+        <v>0.06232147703976701</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.463</v>
+        <v>-0.235</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2650257584430453</v>
+        <v>-0.196652719665272</v>
       </c>
       <c r="AK3">
-        <v>-0.2973667308927425</v>
+        <v>-0.1246684350132626</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.008999999999999999</v>
+        <v>-0.034</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-2.338383838383838</v>
+        <v>-0.4681274900398406</v>
       </c>
       <c r="AQ3">
-        <v>-16.44444444444445</v>
+        <v>-13.38235294117647</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_recreation.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_recreation.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1924586036777757</v>
+        <v>0.1919324237271102</v>
       </c>
       <c r="C2">
-        <v>1.72</v>
+        <v>1.708316282176534</v>
       </c>
       <c r="D2">
-        <v>1.532</v>
+        <v>1.537516282176534</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.0172</v>
       </c>
       <c r="G2">
         <v>0.188</v>
@@ -1451,28 +1451,28 @@
         <v>0.24</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0008651599999999999</v>
       </c>
       <c r="N2">
-        <v>0.24</v>
+        <v>0.23913484</v>
       </c>
       <c r="O2">
-        <v>0.0696</v>
+        <v>0.06934910359999999</v>
       </c>
       <c r="P2">
-        <v>0.1704</v>
+        <v>0.1697857364</v>
       </c>
       <c r="Q2">
-        <v>0.2344</v>
+        <v>0.2337857364</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1924586036777757</v>
+        <v>0.1935103977041517</v>
       </c>
       <c r="T2">
-        <v>0.8969457633378592</v>
+        <v>0.9033784046708884</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>277.4053354292848</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1919324237271102</v>
+        <v>0.1914062437764446</v>
       </c>
       <c r="C3">
-        <v>1.708316282176534</v>
+        <v>1.69667243293299</v>
       </c>
       <c r="D3">
-        <v>1.537516282176534</v>
+        <v>1.54307243293299</v>
       </c>
       <c r="E3">
-        <v>0.0172</v>
+        <v>0.0344</v>
       </c>
       <c r="F3">
-        <v>0.0172</v>
+        <v>0.0344</v>
       </c>
       <c r="G3">
         <v>0.188</v>
@@ -1533,28 +1533,28 @@
         <v>0.24</v>
       </c>
       <c r="M3">
-        <v>0.0008651599999999999</v>
+        <v>0.00173032</v>
       </c>
       <c r="N3">
-        <v>0.23913484</v>
+        <v>0.23826968</v>
       </c>
       <c r="O3">
-        <v>0.06934910359999999</v>
+        <v>0.06909820719999998</v>
       </c>
       <c r="P3">
-        <v>0.1697857364</v>
+        <v>0.1691714728</v>
       </c>
       <c r="Q3">
-        <v>0.2337857364</v>
+        <v>0.2331714728</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1935103977041517</v>
+        <v>0.1945836569147394</v>
       </c>
       <c r="T3">
-        <v>0.9033784046708884</v>
+        <v>0.9099423243984691</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>277.4053354292848</v>
+        <v>138.7026677146424</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1914062437764446</v>
+        <v>0.1908800638257791</v>
       </c>
       <c r="C4">
-        <v>1.69667243293299</v>
+        <v>1.68506888605841</v>
       </c>
       <c r="D4">
-        <v>1.54307243293299</v>
+        <v>1.548668886058411</v>
       </c>
       <c r="E4">
-        <v>0.0344</v>
+        <v>0.0516</v>
       </c>
       <c r="F4">
-        <v>0.0344</v>
+        <v>0.0516</v>
       </c>
       <c r="G4">
         <v>0.188</v>
@@ -1615,28 +1615,28 @@
         <v>0.24</v>
       </c>
       <c r="M4">
-        <v>0.00173032</v>
+        <v>0.00259548</v>
       </c>
       <c r="N4">
-        <v>0.23826968</v>
+        <v>0.23740452</v>
       </c>
       <c r="O4">
-        <v>0.06909820719999998</v>
+        <v>0.06884731079999999</v>
       </c>
       <c r="P4">
-        <v>0.1691714728</v>
+        <v>0.1685572092</v>
       </c>
       <c r="Q4">
-        <v>0.2331714728</v>
+        <v>0.2325572092</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1945836569147394</v>
+        <v>0.1956790451812156</v>
       </c>
       <c r="T4">
-        <v>0.9099423243984691</v>
+        <v>0.916641582677134</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>138.7026677146424</v>
+        <v>92.46844514309491</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1908800638257791</v>
+        <v>0.1903538838751135</v>
       </c>
       <c r="C5">
-        <v>1.68506888605841</v>
+        <v>1.673506081657856</v>
       </c>
       <c r="D5">
-        <v>1.548668886058411</v>
+        <v>1.554306081657856</v>
       </c>
       <c r="E5">
-        <v>0.0516</v>
+        <v>0.0688</v>
       </c>
       <c r="F5">
-        <v>0.0516</v>
+        <v>0.0688</v>
       </c>
       <c r="G5">
         <v>0.188</v>
@@ -1697,28 +1697,28 @@
         <v>0.24</v>
       </c>
       <c r="M5">
-        <v>0.00259548</v>
+        <v>0.00346064</v>
       </c>
       <c r="N5">
-        <v>0.23740452</v>
+        <v>0.23653936</v>
       </c>
       <c r="O5">
-        <v>0.06884731079999999</v>
+        <v>0.0685964144</v>
       </c>
       <c r="P5">
-        <v>0.1685572092</v>
+        <v>0.1679429456</v>
       </c>
       <c r="Q5">
-        <v>0.2325572092</v>
+        <v>0.2319429456</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1956790451812156</v>
+        <v>0.1967972540365766</v>
       </c>
       <c r="T5">
-        <v>0.916641582677134</v>
+        <v>0.9234804088366042</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>92.46844514309491</v>
+        <v>69.35133385732119</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1903538838751135</v>
+        <v>0.189827703924448</v>
       </c>
       <c r="C6">
-        <v>1.673506081657856</v>
+        <v>1.66198446626777</v>
       </c>
       <c r="D6">
-        <v>1.554306081657856</v>
+        <v>1.55998446626777</v>
       </c>
       <c r="E6">
-        <v>0.0688</v>
+        <v>0.08600000000000001</v>
       </c>
       <c r="F6">
-        <v>0.0688</v>
+        <v>0.08600000000000001</v>
       </c>
       <c r="G6">
         <v>0.188</v>
@@ -1779,28 +1779,28 @@
         <v>0.24</v>
       </c>
       <c r="M6">
-        <v>0.00346064</v>
+        <v>0.0043258</v>
       </c>
       <c r="N6">
-        <v>0.23653936</v>
+        <v>0.2356742</v>
       </c>
       <c r="O6">
-        <v>0.0685964144</v>
+        <v>0.06834551799999999</v>
       </c>
       <c r="P6">
-        <v>0.1679429456</v>
+        <v>0.167328682</v>
       </c>
       <c r="Q6">
-        <v>0.2319429456</v>
+        <v>0.231328682</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1967972540365766</v>
+        <v>0.1979390041309979</v>
       </c>
       <c r="T6">
-        <v>0.9234804088366042</v>
+        <v>0.9304632102836423</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>69.35133385732119</v>
+        <v>55.48106708585695</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.189827703924448</v>
+        <v>0.1893015239737824</v>
       </c>
       <c r="C7">
-        <v>1.66198446626777</v>
+        <v>1.650504492973897</v>
       </c>
       <c r="D7">
-        <v>1.55998446626777</v>
+        <v>1.565704492973897</v>
       </c>
       <c r="E7">
-        <v>0.08600000000000001</v>
+        <v>0.1032</v>
       </c>
       <c r="F7">
-        <v>0.08600000000000001</v>
+        <v>0.1032</v>
       </c>
       <c r="G7">
         <v>0.188</v>
@@ -1861,28 +1861,28 @@
         <v>0.24</v>
       </c>
       <c r="M7">
-        <v>0.0043258</v>
+        <v>0.00519096</v>
       </c>
       <c r="N7">
-        <v>0.2356742</v>
+        <v>0.23480904</v>
       </c>
       <c r="O7">
-        <v>0.06834551799999999</v>
+        <v>0.06809462159999999</v>
       </c>
       <c r="P7">
-        <v>0.167328682</v>
+        <v>0.1667144184</v>
       </c>
       <c r="Q7">
-        <v>0.231328682</v>
+        <v>0.2307144184</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1979390041309979</v>
+        <v>0.1991050467806196</v>
       </c>
       <c r="T7">
-        <v>0.9304632102836423</v>
+        <v>0.9375945819742345</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>55.48106708585695</v>
+        <v>46.23422257154746</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1893015239737824</v>
+        <v>0.1887753440231169</v>
       </c>
       <c r="C8">
-        <v>1.650504492973897</v>
+        <v>1.639066621531786</v>
       </c>
       <c r="D8">
-        <v>1.565704492973897</v>
+        <v>1.571466621531787</v>
       </c>
       <c r="E8">
-        <v>0.1032</v>
+        <v>0.1204</v>
       </c>
       <c r="F8">
-        <v>0.1032</v>
+        <v>0.1204</v>
       </c>
       <c r="G8">
         <v>0.188</v>
@@ -1943,28 +1943,28 @@
         <v>0.24</v>
       </c>
       <c r="M8">
-        <v>0.00519096</v>
+        <v>0.006056119999999999</v>
       </c>
       <c r="N8">
-        <v>0.23480904</v>
+        <v>0.23394388</v>
       </c>
       <c r="O8">
-        <v>0.06809462159999999</v>
+        <v>0.0678437252</v>
       </c>
       <c r="P8">
-        <v>0.1667144184</v>
+        <v>0.1661001548</v>
       </c>
       <c r="Q8">
-        <v>0.2307144184</v>
+        <v>0.2301001548</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1991050467806196</v>
+        <v>0.2002961656162547</v>
       </c>
       <c r="T8">
-        <v>0.9375945819742345</v>
+        <v>0.9448793164968825</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.23422257154746</v>
+        <v>39.62933363275497</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1887753440231169</v>
+        <v>0.1882491640724513</v>
       </c>
       <c r="C9">
-        <v>1.639066621531787</v>
+        <v>1.627671318489991</v>
       </c>
       <c r="D9">
-        <v>1.571466621531787</v>
+        <v>1.577271318489991</v>
       </c>
       <c r="E9">
-        <v>0.1204</v>
+        <v>0.1376</v>
       </c>
       <c r="F9">
-        <v>0.1204</v>
+        <v>0.1376</v>
       </c>
       <c r="G9">
         <v>0.188</v>
@@ -2025,28 +2025,28 @@
         <v>0.24</v>
       </c>
       <c r="M9">
-        <v>0.00605612</v>
+        <v>0.006921279999999999</v>
       </c>
       <c r="N9">
-        <v>0.23394388</v>
+        <v>0.23307872</v>
       </c>
       <c r="O9">
-        <v>0.0678437252</v>
+        <v>0.06759282879999999</v>
       </c>
       <c r="P9">
-        <v>0.1661001548</v>
+        <v>0.1654858912</v>
       </c>
       <c r="Q9">
-        <v>0.2301001548</v>
+        <v>0.2294858912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2002961656162547</v>
+        <v>0.201513178339621</v>
       </c>
       <c r="T9">
-        <v>0.9448793164968825</v>
+        <v>0.9523224148135009</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.62933363275496</v>
+        <v>34.6756669286606</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1882491640724513</v>
+        <v>0.1877229841217858</v>
       </c>
       <c r="C10">
-        <v>1.627671318489991</v>
+        <v>1.616319057315981</v>
       </c>
       <c r="D10">
-        <v>1.577271318489991</v>
+        <v>1.583119057315981</v>
       </c>
       <c r="E10">
-        <v>0.1376</v>
+        <v>0.1548</v>
       </c>
       <c r="F10">
-        <v>0.1376</v>
+        <v>0.1548</v>
       </c>
       <c r="G10">
         <v>0.188</v>
@@ -2107,28 +2107,28 @@
         <v>0.24</v>
       </c>
       <c r="M10">
-        <v>0.006921279999999999</v>
+        <v>0.00778644</v>
       </c>
       <c r="N10">
-        <v>0.23307872</v>
+        <v>0.23221356</v>
       </c>
       <c r="O10">
-        <v>0.06759282879999999</v>
+        <v>0.06734193239999998</v>
       </c>
       <c r="P10">
-        <v>0.1654858912</v>
+        <v>0.1648716276</v>
       </c>
       <c r="Q10">
-        <v>0.2294858912</v>
+        <v>0.2288716276</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.201513178339621</v>
+        <v>0.202756938595369</v>
       </c>
       <c r="T10">
-        <v>0.9523224148135009</v>
+        <v>0.9599290977085067</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.6756669286606</v>
+        <v>30.82281504769831</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1877229841217858</v>
+        <v>0.1871968041711202</v>
       </c>
       <c r="C11">
-        <v>1.616319057315981</v>
+        <v>1.605010318524884</v>
       </c>
       <c r="D11">
-        <v>1.583119057315981</v>
+        <v>1.589010318524884</v>
       </c>
       <c r="E11">
-        <v>0.1548</v>
+        <v>0.172</v>
       </c>
       <c r="F11">
-        <v>0.1548</v>
+        <v>0.172</v>
       </c>
       <c r="G11">
         <v>0.188</v>
@@ -2189,28 +2189,28 @@
         <v>0.24</v>
       </c>
       <c r="M11">
-        <v>0.00778644</v>
+        <v>0.008651599999999999</v>
       </c>
       <c r="N11">
-        <v>0.23221356</v>
+        <v>0.2313484</v>
       </c>
       <c r="O11">
-        <v>0.06734193239999998</v>
+        <v>0.06709103599999999</v>
       </c>
       <c r="P11">
-        <v>0.1648716276</v>
+        <v>0.164257364</v>
       </c>
       <c r="Q11">
-        <v>0.2288716276</v>
+        <v>0.228257364</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.202756938595369</v>
+        <v>0.2040283379679114</v>
       </c>
       <c r="T11">
-        <v>0.9599290977085067</v>
+        <v>0.9677048180011791</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.82281504769831</v>
+        <v>27.74053354292848</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1871968041711202</v>
+        <v>0.1866706242204547</v>
       </c>
       <c r="C12">
-        <v>1.605010318524884</v>
+        <v>1.593745589811111</v>
       </c>
       <c r="D12">
-        <v>1.589010318524884</v>
+        <v>1.594945589811111</v>
       </c>
       <c r="E12">
-        <v>0.172</v>
+        <v>0.1892</v>
       </c>
       <c r="F12">
-        <v>0.172</v>
+        <v>0.1892</v>
       </c>
       <c r="G12">
         <v>0.188</v>
@@ -2271,28 +2271,28 @@
         <v>0.24</v>
       </c>
       <c r="M12">
-        <v>0.008651600000000001</v>
+        <v>0.009516759999999999</v>
       </c>
       <c r="N12">
-        <v>0.2313484</v>
+        <v>0.23048324</v>
       </c>
       <c r="O12">
-        <v>0.06709103599999999</v>
+        <v>0.06684013959999999</v>
       </c>
       <c r="P12">
-        <v>0.164257364</v>
+        <v>0.1636431004</v>
       </c>
       <c r="Q12">
-        <v>0.228257364</v>
+        <v>0.2276431004</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2040283379679114</v>
+        <v>0.2053283081128704</v>
       </c>
       <c r="T12">
-        <v>0.9677048180011791</v>
+        <v>0.9756552735813275</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.74053354292847</v>
+        <v>25.2186668572077</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1866706242204547</v>
+        <v>0.1861444442697891</v>
       </c>
       <c r="C13">
-        <v>1.593745589811111</v>
+        <v>1.582525366182933</v>
       </c>
       <c r="D13">
-        <v>1.594945589811111</v>
+        <v>1.600925366182933</v>
       </c>
       <c r="E13">
-        <v>0.1892</v>
+        <v>0.2064</v>
       </c>
       <c r="F13">
-        <v>0.1892</v>
+        <v>0.2064</v>
       </c>
       <c r="G13">
         <v>0.188</v>
@@ -2353,28 +2353,28 @@
         <v>0.24</v>
       </c>
       <c r="M13">
-        <v>0.009516759999999999</v>
+        <v>0.01038192</v>
       </c>
       <c r="N13">
-        <v>0.23048324</v>
+        <v>0.22961808</v>
       </c>
       <c r="O13">
-        <v>0.06684013959999999</v>
+        <v>0.0665892432</v>
       </c>
       <c r="P13">
-        <v>0.1636431004</v>
+        <v>0.1630288368</v>
       </c>
       <c r="Q13">
-        <v>0.2276431004</v>
+        <v>0.2270288368</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2053283081128704</v>
+        <v>0.2066578230338513</v>
       </c>
       <c r="T13">
-        <v>0.9756552735813275</v>
+        <v>0.9837864213337518</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.2186668572077</v>
+        <v>23.11711128577373</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1861444442697891</v>
+        <v>0.1856182643191236</v>
       </c>
       <c r="C14">
-        <v>1.582525366182933</v>
+        <v>1.571350150100109</v>
       </c>
       <c r="D14">
-        <v>1.600925366182933</v>
+        <v>1.606950150100109</v>
       </c>
       <c r="E14">
-        <v>0.2064</v>
+        <v>0.2236</v>
       </c>
       <c r="F14">
-        <v>0.2064</v>
+        <v>0.2236</v>
       </c>
       <c r="G14">
         <v>0.188</v>
@@ -2435,28 +2435,28 @@
         <v>0.24</v>
       </c>
       <c r="M14">
-        <v>0.01038192</v>
+        <v>0.01124708</v>
       </c>
       <c r="N14">
-        <v>0.22961808</v>
+        <v>0.22875292</v>
       </c>
       <c r="O14">
-        <v>0.0665892432</v>
+        <v>0.06633834679999999</v>
       </c>
       <c r="P14">
-        <v>0.1630288368</v>
+        <v>0.1624145732</v>
       </c>
       <c r="Q14">
-        <v>0.2270288368</v>
+        <v>0.2264145732</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2066578230338513</v>
+        <v>0.208017901516234</v>
       </c>
       <c r="T14">
-        <v>0.9837864213337518</v>
+        <v>0.9921044920230138</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.11711128577373</v>
+        <v>21.33887195609883</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1856182643191236</v>
+        <v>0.185092084368458</v>
       </c>
       <c r="C15">
-        <v>1.571350150100109</v>
+        <v>1.560220451614623</v>
       </c>
       <c r="D15">
-        <v>1.606950150100109</v>
+        <v>1.613020451614623</v>
       </c>
       <c r="E15">
-        <v>0.2236</v>
+        <v>0.2408</v>
       </c>
       <c r="F15">
-        <v>0.2236</v>
+        <v>0.2408</v>
       </c>
       <c r="G15">
         <v>0.188</v>
@@ -2517,28 +2517,28 @@
         <v>0.24</v>
       </c>
       <c r="M15">
-        <v>0.01124708</v>
+        <v>0.01211224</v>
       </c>
       <c r="N15">
-        <v>0.22875292</v>
+        <v>0.22788776</v>
       </c>
       <c r="O15">
-        <v>0.06633834679999999</v>
+        <v>0.0660874504</v>
       </c>
       <c r="P15">
-        <v>0.1624145732</v>
+        <v>0.1618003096</v>
       </c>
       <c r="Q15">
-        <v>0.2264145732</v>
+        <v>0.2258003096</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.208017901516234</v>
+        <v>0.2094096097307652</v>
       </c>
       <c r="T15">
-        <v>0.9921044920230138</v>
+        <v>1.000616006216677</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.33887195609883</v>
+        <v>19.81466681637748</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.185092084368458</v>
+        <v>0.1845659044177925</v>
       </c>
       <c r="C16">
-        <v>1.560220451614623</v>
+        <v>1.549136788514628</v>
       </c>
       <c r="D16">
-        <v>1.613020451614623</v>
+        <v>1.619136788514628</v>
       </c>
       <c r="E16">
-        <v>0.2408</v>
+        <v>0.258</v>
       </c>
       <c r="F16">
-        <v>0.2408</v>
+        <v>0.258</v>
       </c>
       <c r="G16">
         <v>0.188</v>
@@ -2599,28 +2599,28 @@
         <v>0.24</v>
       </c>
       <c r="M16">
-        <v>0.01211224</v>
+        <v>0.0129774</v>
       </c>
       <c r="N16">
-        <v>0.22788776</v>
+        <v>0.2270226</v>
       </c>
       <c r="O16">
-        <v>0.0660874504</v>
+        <v>0.06583655399999999</v>
       </c>
       <c r="P16">
-        <v>0.1618003096</v>
+        <v>0.161186046</v>
       </c>
       <c r="Q16">
-        <v>0.2258003096</v>
+        <v>0.225186046</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2094096097307652</v>
+        <v>0.2108340640209324</v>
       </c>
       <c r="T16">
-        <v>1.000616006216677</v>
+        <v>1.009327791332544</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.81466681637748</v>
+        <v>18.49368902861898</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1845659044177925</v>
+        <v>0.1840397244671269</v>
       </c>
       <c r="C17">
-        <v>1.549136788514628</v>
+        <v>1.538099686471677</v>
       </c>
       <c r="D17">
-        <v>1.619136788514628</v>
+        <v>1.625299686471677</v>
       </c>
       <c r="E17">
-        <v>0.258</v>
+        <v>0.2752</v>
       </c>
       <c r="F17">
-        <v>0.258</v>
+        <v>0.2752</v>
       </c>
       <c r="G17">
         <v>0.188</v>
@@ -2681,28 +2681,28 @@
         <v>0.24</v>
       </c>
       <c r="M17">
-        <v>0.0129774</v>
+        <v>0.01384256</v>
       </c>
       <c r="N17">
-        <v>0.2270226</v>
+        <v>0.22615744</v>
       </c>
       <c r="O17">
-        <v>0.06583655399999999</v>
+        <v>0.06558565759999999</v>
       </c>
       <c r="P17">
-        <v>0.161186046</v>
+        <v>0.1605717824</v>
       </c>
       <c r="Q17">
-        <v>0.225186046</v>
+        <v>0.2245717824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2108340640209324</v>
+        <v>0.2122924338894368</v>
       </c>
       <c r="T17">
-        <v>1.009327791332544</v>
+        <v>1.018246999903551</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.49368902861898</v>
+        <v>17.3378334643303</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1840397244671269</v>
+        <v>0.1835135445164614</v>
       </c>
       <c r="C18">
-        <v>1.538099686471677</v>
+        <v>1.527109679191327</v>
       </c>
       <c r="D18">
-        <v>1.625299686471677</v>
+        <v>1.631509679191327</v>
       </c>
       <c r="E18">
-        <v>0.2752</v>
+        <v>0.2924</v>
       </c>
       <c r="F18">
-        <v>0.2752</v>
+        <v>0.2924</v>
       </c>
       <c r="G18">
         <v>0.188</v>
@@ -2763,28 +2763,28 @@
         <v>0.24</v>
       </c>
       <c r="M18">
-        <v>0.01384256</v>
+        <v>0.01470772</v>
       </c>
       <c r="N18">
-        <v>0.22615744</v>
+        <v>0.22529228</v>
       </c>
       <c r="O18">
-        <v>0.06558565759999999</v>
+        <v>0.06533476119999999</v>
       </c>
       <c r="P18">
-        <v>0.1605717824</v>
+        <v>0.1599575188</v>
       </c>
       <c r="Q18">
-        <v>0.2245717824</v>
+        <v>0.2239575188</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2122924338894368</v>
+        <v>0.2137859452005559</v>
       </c>
       <c r="T18">
-        <v>1.018246999903551</v>
+        <v>1.027381129163015</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.3378334643303</v>
+        <v>16.31796090760498</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1835135445164614</v>
+        <v>0.1829873645657958</v>
       </c>
       <c r="C19">
-        <v>1.527109679191327</v>
+        <v>1.516167308567212</v>
       </c>
       <c r="D19">
-        <v>1.631509679191327</v>
+        <v>1.637767308567212</v>
       </c>
       <c r="E19">
-        <v>0.2924</v>
+        <v>0.3096</v>
       </c>
       <c r="F19">
-        <v>0.2924</v>
+        <v>0.3096</v>
       </c>
       <c r="G19">
         <v>0.188</v>
@@ -2845,28 +2845,28 @@
         <v>0.24</v>
       </c>
       <c r="M19">
-        <v>0.01470772</v>
+        <v>0.01557288</v>
       </c>
       <c r="N19">
-        <v>0.22529228</v>
+        <v>0.22442712</v>
       </c>
       <c r="O19">
-        <v>0.06533476119999999</v>
+        <v>0.06508386479999999</v>
       </c>
       <c r="P19">
-        <v>0.1599575188</v>
+        <v>0.1593432552</v>
       </c>
       <c r="Q19">
-        <v>0.2239575188</v>
+        <v>0.2233432552</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2137859452005559</v>
+        <v>0.2153158836168242</v>
       </c>
       <c r="T19">
-        <v>1.027381129163015</v>
+        <v>1.036738042062955</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.31796090760498</v>
+        <v>15.41140752384915</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1829873645657958</v>
+        <v>0.1824611846151303</v>
       </c>
       <c r="C20">
-        <v>1.516167308567212</v>
+        <v>1.505273124838676</v>
       </c>
       <c r="D20">
-        <v>1.637767308567212</v>
+        <v>1.644073124838676</v>
       </c>
       <c r="E20">
-        <v>0.3096</v>
+        <v>0.3268</v>
       </c>
       <c r="F20">
-        <v>0.3096</v>
+        <v>0.3268</v>
       </c>
       <c r="G20">
         <v>0.188</v>
@@ -2927,28 +2927,28 @@
         <v>0.24</v>
       </c>
       <c r="M20">
-        <v>0.01557288</v>
+        <v>0.01643804</v>
       </c>
       <c r="N20">
-        <v>0.22442712</v>
+        <v>0.22356196</v>
       </c>
       <c r="O20">
-        <v>0.06508386479999999</v>
+        <v>0.0648329684</v>
       </c>
       <c r="P20">
-        <v>0.1593432552</v>
+        <v>0.1587289916</v>
       </c>
       <c r="Q20">
-        <v>0.2233432552</v>
+        <v>0.2227289916</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2153158836168242</v>
+        <v>0.2168835982902843</v>
       </c>
       <c r="T20">
-        <v>1.036738042062955</v>
+        <v>1.046325989849312</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.41140752384915</v>
+        <v>14.60028081206762</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1824611846151303</v>
+        <v>0.1819350046644647</v>
       </c>
       <c r="C21">
-        <v>1.505273124838676</v>
+        <v>1.494427686752052</v>
       </c>
       <c r="D21">
-        <v>1.644073124838676</v>
+        <v>1.650427686752052</v>
       </c>
       <c r="E21">
-        <v>0.3268</v>
+        <v>0.344</v>
       </c>
       <c r="F21">
-        <v>0.3268</v>
+        <v>0.344</v>
       </c>
       <c r="G21">
         <v>0.188</v>
@@ -3009,28 +3009,28 @@
         <v>0.24</v>
       </c>
       <c r="M21">
-        <v>0.01643804</v>
+        <v>0.0173032</v>
       </c>
       <c r="N21">
-        <v>0.22356196</v>
+        <v>0.2226968</v>
       </c>
       <c r="O21">
-        <v>0.0648329684</v>
+        <v>0.06458207199999999</v>
       </c>
       <c r="P21">
-        <v>0.1587289916</v>
+        <v>0.158114728</v>
       </c>
       <c r="Q21">
-        <v>0.2227289916</v>
+        <v>0.222114728</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2168835982902843</v>
+        <v>0.2184905058305809</v>
       </c>
       <c r="T21">
-        <v>1.046325989849312</v>
+        <v>1.056153636330329</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.60028081206762</v>
+        <v>13.87026677146424</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1819350046644647</v>
+        <v>0.1814088247137992</v>
       </c>
       <c r="C22">
-        <v>1.494427686752052</v>
+        <v>1.483631561725713</v>
       </c>
       <c r="D22">
-        <v>1.650427686752052</v>
+        <v>1.656831561725713</v>
       </c>
       <c r="E22">
-        <v>0.344</v>
+        <v>0.3612</v>
       </c>
       <c r="F22">
-        <v>0.344</v>
+        <v>0.3612</v>
       </c>
       <c r="G22">
         <v>0.188</v>
@@ -3091,28 +3091,28 @@
         <v>0.24</v>
       </c>
       <c r="M22">
-        <v>0.0173032</v>
+        <v>0.01816836</v>
       </c>
       <c r="N22">
-        <v>0.2226968</v>
+        <v>0.22183164</v>
       </c>
       <c r="O22">
-        <v>0.06458207199999999</v>
+        <v>0.0643311756</v>
       </c>
       <c r="P22">
-        <v>0.158114728</v>
+        <v>0.1575004644</v>
       </c>
       <c r="Q22">
-        <v>0.222114728</v>
+        <v>0.2215004644</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2184905058305809</v>
+        <v>0.2201380945744293</v>
       </c>
       <c r="T22">
-        <v>1.056153636330329</v>
+        <v>1.066230083988081</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.87026677146424</v>
+        <v>13.20977787758499</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1814088247137992</v>
+        <v>0.1811169447631337</v>
       </c>
       <c r="C23">
-        <v>1.483631561725713</v>
+        <v>1.470005363331596</v>
       </c>
       <c r="D23">
-        <v>1.656831561725713</v>
+        <v>1.660405363331596</v>
       </c>
       <c r="E23">
-        <v>0.3612</v>
+        <v>0.3784</v>
       </c>
       <c r="F23">
-        <v>0.3612</v>
+        <v>0.3784</v>
       </c>
       <c r="G23">
         <v>0.188</v>
@@ -3173,45 +3173,45 @@
         <v>0.24</v>
       </c>
       <c r="M23">
-        <v>0.01816836</v>
+        <v>0.01960112</v>
       </c>
       <c r="N23">
-        <v>0.22183164</v>
+        <v>0.22039888</v>
       </c>
       <c r="O23">
-        <v>0.0643311756</v>
+        <v>0.06391567519999999</v>
       </c>
       <c r="P23">
-        <v>0.1575004644</v>
+        <v>0.1564832048</v>
       </c>
       <c r="Q23">
-        <v>0.2215004644</v>
+        <v>0.2204832048</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2201380945744293</v>
+        <v>0.2218279291835047</v>
       </c>
       <c r="T23">
-        <v>1.066230083988081</v>
+        <v>1.076564902098595</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.29</v>
       </c>
       <c r="W23">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.20977787758499</v>
+        <v>12.24419829070992</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1811169447631337</v>
+        <v>0.1806014148124681</v>
       </c>
       <c r="C24">
-        <v>1.470005363331596</v>
+        <v>1.459155361187582</v>
       </c>
       <c r="D24">
-        <v>1.660405363331596</v>
+        <v>1.666755361187582</v>
       </c>
       <c r="E24">
-        <v>0.3784</v>
+        <v>0.3956</v>
       </c>
       <c r="F24">
-        <v>0.3784</v>
+        <v>0.3956</v>
       </c>
       <c r="G24">
         <v>0.188</v>
@@ -3255,28 +3255,28 @@
         <v>0.24</v>
       </c>
       <c r="M24">
-        <v>0.01960112</v>
+        <v>0.02049208</v>
       </c>
       <c r="N24">
-        <v>0.22039888</v>
+        <v>0.21950792</v>
       </c>
       <c r="O24">
-        <v>0.06391567519999999</v>
+        <v>0.0636572968</v>
       </c>
       <c r="P24">
-        <v>0.1564832048</v>
+        <v>0.1558506232</v>
       </c>
       <c r="Q24">
-        <v>0.2204832048</v>
+        <v>0.2198506232</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2218279291835047</v>
+        <v>0.2235616556006079</v>
       </c>
       <c r="T24">
-        <v>1.076564902098595</v>
+        <v>1.087168157043148</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.24419829070992</v>
+        <v>11.71184184328775</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1806014148124681</v>
+        <v>0.1800858848618025</v>
       </c>
       <c r="C25">
-        <v>1.459155361187582</v>
+        <v>1.448354114936041</v>
       </c>
       <c r="D25">
-        <v>1.666755361187582</v>
+        <v>1.673154114936041</v>
       </c>
       <c r="E25">
-        <v>0.3956</v>
+        <v>0.4128</v>
       </c>
       <c r="F25">
-        <v>0.3956</v>
+        <v>0.4128</v>
       </c>
       <c r="G25">
         <v>0.188</v>
@@ -3337,28 +3337,28 @@
         <v>0.24</v>
       </c>
       <c r="M25">
-        <v>0.02049208</v>
+        <v>0.02138304</v>
       </c>
       <c r="N25">
-        <v>0.21950792</v>
+        <v>0.21861696</v>
       </c>
       <c r="O25">
-        <v>0.0636572968</v>
+        <v>0.06339891839999999</v>
       </c>
       <c r="P25">
-        <v>0.1558506232</v>
+        <v>0.1552180416</v>
       </c>
       <c r="Q25">
-        <v>0.2198506232</v>
+        <v>0.2192180416</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2235616556006079</v>
+        <v>0.2253410063971086</v>
       </c>
       <c r="T25">
-        <v>1.087168157043148</v>
+        <v>1.098050445012558</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.71184184328775</v>
+        <v>11.22384843315076</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1800858848618025</v>
+        <v>0.179570354911137</v>
       </c>
       <c r="C26">
-        <v>1.448354114936041</v>
+        <v>1.437602188269643</v>
       </c>
       <c r="D26">
-        <v>1.673154114936041</v>
+        <v>1.679602188269643</v>
       </c>
       <c r="E26">
-        <v>0.4128</v>
+        <v>0.43</v>
       </c>
       <c r="F26">
-        <v>0.4128</v>
+        <v>0.43</v>
       </c>
       <c r="G26">
         <v>0.188</v>
@@ -3419,28 +3419,28 @@
         <v>0.24</v>
       </c>
       <c r="M26">
-        <v>0.02138304</v>
+        <v>0.022274</v>
       </c>
       <c r="N26">
-        <v>0.21861696</v>
+        <v>0.217726</v>
       </c>
       <c r="O26">
-        <v>0.06339891839999999</v>
+        <v>0.06314054</v>
       </c>
       <c r="P26">
-        <v>0.1552180416</v>
+        <v>0.15458546</v>
       </c>
       <c r="Q26">
-        <v>0.2192180416</v>
+        <v>0.21858546</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2253410063971086</v>
+        <v>0.2271678065481826</v>
       </c>
       <c r="T26">
-        <v>1.098050445012558</v>
+        <v>1.109222927327819</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.22384843315076</v>
+        <v>10.77489449582473</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.179570354911137</v>
+        <v>0.1790548249604715</v>
       </c>
       <c r="C27">
-        <v>1.437602188269643</v>
+        <v>1.426900153604205</v>
       </c>
       <c r="D27">
-        <v>1.679602188269643</v>
+        <v>1.686100153604206</v>
       </c>
       <c r="E27">
-        <v>0.43</v>
+        <v>0.4472</v>
       </c>
       <c r="F27">
-        <v>0.43</v>
+        <v>0.4472</v>
       </c>
       <c r="G27">
         <v>0.188</v>
@@ -3501,28 +3501,28 @@
         <v>0.24</v>
       </c>
       <c r="M27">
-        <v>0.022274</v>
+        <v>0.02316496</v>
       </c>
       <c r="N27">
-        <v>0.217726</v>
+        <v>0.21683504</v>
       </c>
       <c r="O27">
-        <v>0.06314054</v>
+        <v>0.06288216159999999</v>
       </c>
       <c r="P27">
-        <v>0.15458546</v>
+        <v>0.1539528784</v>
       </c>
       <c r="Q27">
-        <v>0.21858546</v>
+        <v>0.2179528784</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2271678065481826</v>
+        <v>0.2290439796763128</v>
       </c>
       <c r="T27">
-        <v>1.109222927327819</v>
+        <v>1.120697368624574</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.77489449582473</v>
+        <v>10.36047547675455</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1790548249604715</v>
+        <v>0.1785392950098059</v>
       </c>
       <c r="C28">
-        <v>1.426900153604205</v>
+        <v>1.416248592248094</v>
       </c>
       <c r="D28">
-        <v>1.686100153604206</v>
+        <v>1.692648592248094</v>
       </c>
       <c r="E28">
-        <v>0.4472</v>
+        <v>0.4644</v>
       </c>
       <c r="F28">
-        <v>0.4472</v>
+        <v>0.4644</v>
       </c>
       <c r="G28">
         <v>0.188</v>
@@ -3583,28 +3583,28 @@
         <v>0.24</v>
       </c>
       <c r="M28">
-        <v>0.02316496</v>
+        <v>0.02405592</v>
       </c>
       <c r="N28">
-        <v>0.21683504</v>
+        <v>0.21594408</v>
       </c>
       <c r="O28">
-        <v>0.06288216159999999</v>
+        <v>0.06262378319999999</v>
       </c>
       <c r="P28">
-        <v>0.1539528784</v>
+        <v>0.1533202968</v>
       </c>
       <c r="Q28">
-        <v>0.2179528784</v>
+        <v>0.2173202968</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2290439796763128</v>
+        <v>0.2309715548079533</v>
       </c>
       <c r="T28">
-        <v>1.120697368624574</v>
+        <v>1.132486178176034</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.36047547675455</v>
+        <v>9.976754162800674</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1785392950098059</v>
+        <v>0.1783617250591403</v>
       </c>
       <c r="C29">
-        <v>1.416248592248094</v>
+        <v>1.401315939982786</v>
       </c>
       <c r="D29">
-        <v>1.692648592248094</v>
+        <v>1.694915939982786</v>
       </c>
       <c r="E29">
-        <v>0.4644</v>
+        <v>0.4816</v>
       </c>
       <c r="F29">
-        <v>0.4644</v>
+        <v>0.4816</v>
       </c>
       <c r="G29">
         <v>0.188</v>
@@ -3665,45 +3665,45 @@
         <v>0.24</v>
       </c>
       <c r="M29">
-        <v>0.02405592</v>
+        <v>0.0257656</v>
       </c>
       <c r="N29">
-        <v>0.21594408</v>
+        <v>0.2142344</v>
       </c>
       <c r="O29">
-        <v>0.06262378319999999</v>
+        <v>0.06212797599999999</v>
       </c>
       <c r="P29">
-        <v>0.1533202968</v>
+        <v>0.152106424</v>
       </c>
       <c r="Q29">
-        <v>0.2173202968</v>
+        <v>0.216106424</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2309715548079533</v>
+        <v>0.2329526736932505</v>
       </c>
       <c r="T29">
-        <v>1.132486178176034</v>
+        <v>1.144602454659479</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.29</v>
       </c>
       <c r="W29">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.976754162800674</v>
+        <v>9.314745241717638</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1783617250591403</v>
+        <v>0.1778582651084748</v>
       </c>
       <c r="C30">
-        <v>1.401315939982786</v>
+        <v>1.390577650613506</v>
       </c>
       <c r="D30">
-        <v>1.694915939982786</v>
+        <v>1.701377650613507</v>
       </c>
       <c r="E30">
-        <v>0.4816</v>
+        <v>0.4988000000000001</v>
       </c>
       <c r="F30">
-        <v>0.4816</v>
+        <v>0.4988000000000001</v>
       </c>
       <c r="G30">
         <v>0.188</v>
@@ -3747,28 +3747,28 @@
         <v>0.24</v>
       </c>
       <c r="M30">
-        <v>0.0257656</v>
+        <v>0.0266858</v>
       </c>
       <c r="N30">
-        <v>0.2142344</v>
+        <v>0.2133142</v>
       </c>
       <c r="O30">
-        <v>0.06212797599999999</v>
+        <v>0.06186111799999999</v>
       </c>
       <c r="P30">
-        <v>0.152106424</v>
+        <v>0.151453082</v>
       </c>
       <c r="Q30">
-        <v>0.216106424</v>
+        <v>0.215453082</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2329526736932505</v>
+        <v>0.2349895987443307</v>
       </c>
       <c r="T30">
-        <v>1.144602454659479</v>
+        <v>1.157060034705838</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.314745241717638</v>
+        <v>8.993547129934271</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1778582651084748</v>
+        <v>0.1773548051578092</v>
       </c>
       <c r="C31">
-        <v>1.390577650613507</v>
+        <v>1.379888819149037</v>
       </c>
       <c r="D31">
-        <v>1.701377650613507</v>
+        <v>1.707888819149037</v>
       </c>
       <c r="E31">
-        <v>0.4988</v>
+        <v>0.516</v>
       </c>
       <c r="F31">
-        <v>0.4988</v>
+        <v>0.516</v>
       </c>
       <c r="G31">
         <v>0.188</v>
@@ -3829,28 +3829,28 @@
         <v>0.24</v>
       </c>
       <c r="M31">
-        <v>0.0266858</v>
+        <v>0.027606</v>
       </c>
       <c r="N31">
-        <v>0.2133142</v>
+        <v>0.212394</v>
       </c>
       <c r="O31">
-        <v>0.06186111799999999</v>
+        <v>0.06159426</v>
       </c>
       <c r="P31">
-        <v>0.151453082</v>
+        <v>0.15079974</v>
       </c>
       <c r="Q31">
-        <v>0.215453082</v>
+        <v>0.21479974</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2349895987443307</v>
+        <v>0.2370847216540132</v>
       </c>
       <c r="T31">
-        <v>1.157060034705838</v>
+        <v>1.169873545610665</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.993547129934271</v>
+        <v>8.69376222560313</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1773548051578092</v>
+        <v>0.1768513452071437</v>
       </c>
       <c r="C32">
-        <v>1.379888819149037</v>
+        <v>1.369250015596673</v>
       </c>
       <c r="D32">
-        <v>1.707888819149037</v>
+        <v>1.714450015596673</v>
       </c>
       <c r="E32">
-        <v>0.516</v>
+        <v>0.5332</v>
       </c>
       <c r="F32">
-        <v>0.516</v>
+        <v>0.5332</v>
       </c>
       <c r="G32">
         <v>0.188</v>
@@ -3911,28 +3911,28 @@
         <v>0.24</v>
       </c>
       <c r="M32">
-        <v>0.027606</v>
+        <v>0.0285262</v>
       </c>
       <c r="N32">
-        <v>0.212394</v>
+        <v>0.2114738</v>
       </c>
       <c r="O32">
-        <v>0.06159426</v>
+        <v>0.061327402</v>
       </c>
       <c r="P32">
-        <v>0.15079974</v>
+        <v>0.150146398</v>
       </c>
       <c r="Q32">
-        <v>0.21479974</v>
+        <v>0.214146398</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2370847216540132</v>
+        <v>0.2392405727639764</v>
       </c>
       <c r="T32">
-        <v>1.169873545610665</v>
+        <v>1.183058462628675</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.69376222560313</v>
+        <v>8.413318282841738</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1768513452071437</v>
+        <v>0.1763478852564781</v>
       </c>
       <c r="C33">
-        <v>1.369250015596673</v>
+        <v>1.358661818756679</v>
       </c>
       <c r="D33">
-        <v>1.714450015596673</v>
+        <v>1.721061818756679</v>
       </c>
       <c r="E33">
-        <v>0.5332</v>
+        <v>0.5504</v>
       </c>
       <c r="F33">
-        <v>0.5332</v>
+        <v>0.5504</v>
       </c>
       <c r="G33">
         <v>0.188</v>
@@ -3993,28 +3993,28 @@
         <v>0.24</v>
       </c>
       <c r="M33">
-        <v>0.0285262</v>
+        <v>0.0294464</v>
       </c>
       <c r="N33">
-        <v>0.2114738</v>
+        <v>0.2105536</v>
       </c>
       <c r="O33">
-        <v>0.061327402</v>
+        <v>0.06106054399999999</v>
       </c>
       <c r="P33">
-        <v>0.150146398</v>
+        <v>0.149493056</v>
       </c>
       <c r="Q33">
-        <v>0.214146398</v>
+        <v>0.213493056</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2392405727639764</v>
+        <v>0.2414598312595267</v>
       </c>
       <c r="T33">
-        <v>1.183058462628675</v>
+        <v>1.196631171323685</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.413318282841738</v>
+        <v>8.150402086502933</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1763478852564781</v>
+        <v>0.1758444253058126</v>
       </c>
       <c r="C34">
-        <v>1.358661818756679</v>
+        <v>1.348124816392494</v>
       </c>
       <c r="D34">
-        <v>1.721061818756679</v>
+        <v>1.727724816392494</v>
       </c>
       <c r="E34">
-        <v>0.5504</v>
+        <v>0.5676</v>
       </c>
       <c r="F34">
-        <v>0.5504</v>
+        <v>0.5676</v>
       </c>
       <c r="G34">
         <v>0.188</v>
@@ -4075,28 +4075,28 @@
         <v>0.24</v>
       </c>
       <c r="M34">
-        <v>0.0294464</v>
+        <v>0.0303666</v>
       </c>
       <c r="N34">
-        <v>0.2105536</v>
+        <v>0.2096334</v>
       </c>
       <c r="O34">
-        <v>0.06106054399999999</v>
+        <v>0.06079368599999999</v>
       </c>
       <c r="P34">
-        <v>0.149493056</v>
+        <v>0.148839714</v>
       </c>
       <c r="Q34">
-        <v>0.213493056</v>
+        <v>0.212839714</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2414598312595267</v>
+        <v>0.2437453362773322</v>
       </c>
       <c r="T34">
-        <v>1.196631171323685</v>
+        <v>1.210609035502129</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.150402086502933</v>
+        <v>7.903420205093754</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1758444253058126</v>
+        <v>0.175340965355147</v>
       </c>
       <c r="C35">
-        <v>1.348124816392494</v>
+        <v>1.33763960540491</v>
       </c>
       <c r="D35">
-        <v>1.727724816392494</v>
+        <v>1.73443960540491</v>
       </c>
       <c r="E35">
-        <v>0.5676</v>
+        <v>0.5848</v>
       </c>
       <c r="F35">
-        <v>0.5676</v>
+        <v>0.5848</v>
       </c>
       <c r="G35">
         <v>0.188</v>
@@ -4157,28 +4157,28 @@
         <v>0.24</v>
       </c>
       <c r="M35">
-        <v>0.0303666</v>
+        <v>0.0312868</v>
       </c>
       <c r="N35">
-        <v>0.2096334</v>
+        <v>0.2087132</v>
       </c>
       <c r="O35">
-        <v>0.06079368599999999</v>
+        <v>0.06052682799999999</v>
       </c>
       <c r="P35">
-        <v>0.148839714</v>
+        <v>0.148186372</v>
       </c>
       <c r="Q35">
-        <v>0.212839714</v>
+        <v>0.212186372</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2437453362773322</v>
+        <v>0.2461000990229501</v>
       </c>
       <c r="T35">
-        <v>1.210609035502129</v>
+        <v>1.225010471322343</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.903420205093754</v>
+        <v>7.670966669649821</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.175340965355147</v>
+        <v>0.1750363054044815</v>
       </c>
       <c r="C36">
-        <v>1.33763960540491</v>
+        <v>1.324528350304892</v>
       </c>
       <c r="D36">
-        <v>1.73443960540491</v>
+        <v>1.738528350304892</v>
       </c>
       <c r="E36">
-        <v>0.5848</v>
+        <v>0.6020000000000001</v>
       </c>
       <c r="F36">
-        <v>0.5848</v>
+        <v>0.6020000000000001</v>
       </c>
       <c r="G36">
         <v>0.188</v>
@@ -4239,45 +4239,45 @@
         <v>0.24</v>
       </c>
       <c r="M36">
-        <v>0.0312868</v>
+        <v>0.03268860000000001</v>
       </c>
       <c r="N36">
-        <v>0.2087132</v>
+        <v>0.2073114</v>
       </c>
       <c r="O36">
-        <v>0.06052682799999999</v>
+        <v>0.06012030599999999</v>
       </c>
       <c r="P36">
-        <v>0.148186372</v>
+        <v>0.147191094</v>
       </c>
       <c r="Q36">
-        <v>0.212186372</v>
+        <v>0.211191094</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2461000990229501</v>
+        <v>0.2485273160068946</v>
       </c>
       <c r="T36">
-        <v>1.225010471322343</v>
+        <v>1.239855028244718</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.29</v>
       </c>
       <c r="W36">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.670966669649821</v>
+        <v>7.342009140801379</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1750363054044815</v>
+        <v>0.1745385254538159</v>
       </c>
       <c r="C37">
-        <v>1.324528350304892</v>
+        <v>1.314050538192277</v>
       </c>
       <c r="D37">
-        <v>1.738528350304892</v>
+        <v>1.745250538192278</v>
       </c>
       <c r="E37">
-        <v>0.6020000000000001</v>
+        <v>0.6192000000000001</v>
       </c>
       <c r="F37">
-        <v>0.6020000000000001</v>
+        <v>0.6192000000000001</v>
       </c>
       <c r="G37">
         <v>0.188</v>
@@ -4321,28 +4321,28 @@
         <v>0.24</v>
       </c>
       <c r="M37">
-        <v>0.03268860000000001</v>
+        <v>0.03362256</v>
       </c>
       <c r="N37">
-        <v>0.2073114</v>
+        <v>0.20637744</v>
       </c>
       <c r="O37">
-        <v>0.06012030599999999</v>
+        <v>0.0598494576</v>
       </c>
       <c r="P37">
-        <v>0.147191094</v>
+        <v>0.1465279824</v>
       </c>
       <c r="Q37">
-        <v>0.211191094</v>
+        <v>0.2105279824</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2485273160068946</v>
+        <v>0.2510303835215874</v>
       </c>
       <c r="T37">
-        <v>1.239855028244718</v>
+        <v>1.255163477570917</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.342009140801379</v>
+        <v>7.138064442445786</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1745385254538159</v>
+        <v>0.1740407455031504</v>
       </c>
       <c r="C38">
-        <v>1.314050538192277</v>
+        <v>1.303624911839216</v>
       </c>
       <c r="D38">
-        <v>1.745250538192277</v>
+        <v>1.752024911839216</v>
       </c>
       <c r="E38">
-        <v>0.6192</v>
+        <v>0.6364</v>
       </c>
       <c r="F38">
-        <v>0.6192</v>
+        <v>0.6364</v>
       </c>
       <c r="G38">
         <v>0.188</v>
@@ -4403,28 +4403,28 @@
         <v>0.24</v>
       </c>
       <c r="M38">
-        <v>0.03362256</v>
+        <v>0.03455652</v>
       </c>
       <c r="N38">
-        <v>0.20637744</v>
+        <v>0.20544348</v>
       </c>
       <c r="O38">
-        <v>0.0598494576</v>
+        <v>0.05957860919999999</v>
       </c>
       <c r="P38">
-        <v>0.1465279824</v>
+        <v>0.1458648708</v>
       </c>
       <c r="Q38">
-        <v>0.2105279824</v>
+        <v>0.2098648708</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2510303835215874</v>
+        <v>0.2536129134970641</v>
       </c>
       <c r="T38">
-        <v>1.255163477570917</v>
+        <v>1.270957909415408</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.138064442445787</v>
+        <v>6.945143781839143</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1740407455031504</v>
+        <v>0.1735429655524849</v>
       </c>
       <c r="C39">
-        <v>1.303624911839216</v>
+        <v>1.293252081307282</v>
       </c>
       <c r="D39">
-        <v>1.752024911839216</v>
+        <v>1.758852081307282</v>
       </c>
       <c r="E39">
-        <v>0.6364</v>
+        <v>0.6536</v>
       </c>
       <c r="F39">
-        <v>0.6364</v>
+        <v>0.6536</v>
       </c>
       <c r="G39">
         <v>0.188</v>
@@ -4485,28 +4485,28 @@
         <v>0.24</v>
       </c>
       <c r="M39">
-        <v>0.03455652</v>
+        <v>0.03549048</v>
       </c>
       <c r="N39">
-        <v>0.20544348</v>
+        <v>0.20450952</v>
       </c>
       <c r="O39">
-        <v>0.05957860919999999</v>
+        <v>0.0593077608</v>
       </c>
       <c r="P39">
-        <v>0.1458648708</v>
+        <v>0.1452017592</v>
       </c>
       <c r="Q39">
-        <v>0.2098648708</v>
+        <v>0.2092017592</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2536129134970641</v>
+        <v>0.2562787508911046</v>
       </c>
       <c r="T39">
-        <v>1.270957909415408</v>
+        <v>1.287261839061334</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.945143781839143</v>
+        <v>6.762376840211798</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1735429655524849</v>
+        <v>0.1730451856018193</v>
       </c>
       <c r="C40">
-        <v>1.293252081307282</v>
+        <v>1.28293266620423</v>
       </c>
       <c r="D40">
-        <v>1.758852081307282</v>
+        <v>1.76573266620423</v>
       </c>
       <c r="E40">
-        <v>0.6536</v>
+        <v>0.6708000000000001</v>
       </c>
       <c r="F40">
-        <v>0.6536</v>
+        <v>0.6708000000000001</v>
       </c>
       <c r="G40">
         <v>0.188</v>
@@ -4567,28 +4567,28 @@
         <v>0.24</v>
       </c>
       <c r="M40">
-        <v>0.03549048</v>
+        <v>0.03642444</v>
       </c>
       <c r="N40">
-        <v>0.20450952</v>
+        <v>0.20357556</v>
       </c>
       <c r="O40">
-        <v>0.0593077608</v>
+        <v>0.0590369124</v>
       </c>
       <c r="P40">
-        <v>0.1452017592</v>
+        <v>0.1445386476</v>
       </c>
       <c r="Q40">
-        <v>0.2092017592</v>
+        <v>0.2085386476</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2562787508911046</v>
+        <v>0.2590319927898677</v>
       </c>
       <c r="T40">
-        <v>1.287261839061334</v>
+        <v>1.304100323777619</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.762376840211798</v>
+        <v>6.588982562257648</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1730451856018193</v>
+        <v>0.1725474056511537</v>
       </c>
       <c r="C41">
-        <v>1.28293266620423</v>
+        <v>1.27266729587145</v>
       </c>
       <c r="D41">
-        <v>1.76573266620423</v>
+        <v>1.77266729587145</v>
       </c>
       <c r="E41">
-        <v>0.6708000000000001</v>
+        <v>0.6880000000000001</v>
       </c>
       <c r="F41">
-        <v>0.6708000000000001</v>
+        <v>0.6880000000000001</v>
       </c>
       <c r="G41">
         <v>0.188</v>
@@ -4649,28 +4649,28 @@
         <v>0.24</v>
       </c>
       <c r="M41">
-        <v>0.03642444</v>
+        <v>0.03735840000000001</v>
       </c>
       <c r="N41">
-        <v>0.20357556</v>
+        <v>0.2026416</v>
       </c>
       <c r="O41">
-        <v>0.0590369124</v>
+        <v>0.05876606399999999</v>
       </c>
       <c r="P41">
-        <v>0.1445386476</v>
+        <v>0.143875536</v>
       </c>
       <c r="Q41">
-        <v>0.2085386476</v>
+        <v>0.207875536</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2590319927898677</v>
+        <v>0.2618770094185895</v>
       </c>
       <c r="T41">
-        <v>1.304100323777619</v>
+        <v>1.321500091317779</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.588982562257648</v>
+        <v>6.424257998201206</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1725474056511537</v>
+        <v>0.1720496257004882</v>
       </c>
       <c r="C42">
-        <v>1.27266729587145</v>
+        <v>1.262456609575862</v>
       </c>
       <c r="D42">
-        <v>1.77266729587145</v>
+        <v>1.779656609575862</v>
       </c>
       <c r="E42">
-        <v>0.6880000000000001</v>
+        <v>0.7052</v>
       </c>
       <c r="F42">
-        <v>0.6880000000000001</v>
+        <v>0.7052</v>
       </c>
       <c r="G42">
         <v>0.188</v>
@@ -4731,28 +4731,28 @@
         <v>0.24</v>
       </c>
       <c r="M42">
-        <v>0.03735840000000001</v>
+        <v>0.03829236</v>
       </c>
       <c r="N42">
-        <v>0.2026416</v>
+        <v>0.20170764</v>
       </c>
       <c r="O42">
-        <v>0.05876606399999999</v>
+        <v>0.0584952156</v>
       </c>
       <c r="P42">
-        <v>0.143875536</v>
+        <v>0.1432124244</v>
       </c>
       <c r="Q42">
-        <v>0.207875536</v>
+        <v>0.2072124244</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2618770094185895</v>
+        <v>0.264818467288963</v>
       </c>
       <c r="T42">
-        <v>1.321500091317779</v>
+        <v>1.33948968148642</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.424257998201206</v>
+        <v>6.267568778732885</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1720496257004882</v>
+        <v>0.1715518457498226</v>
       </c>
       <c r="C43">
-        <v>1.262456609575862</v>
+        <v>1.25230125670636</v>
       </c>
       <c r="D43">
-        <v>1.779656609575862</v>
+        <v>1.78670125670636</v>
       </c>
       <c r="E43">
-        <v>0.7052</v>
+        <v>0.7224</v>
       </c>
       <c r="F43">
-        <v>0.7052</v>
+        <v>0.7224</v>
       </c>
       <c r="G43">
         <v>0.188</v>
@@ -4813,28 +4813,28 @@
         <v>0.24</v>
       </c>
       <c r="M43">
-        <v>0.03829236</v>
+        <v>0.03922632</v>
       </c>
       <c r="N43">
-        <v>0.20170764</v>
+        <v>0.20077368</v>
       </c>
       <c r="O43">
-        <v>0.0584952156</v>
+        <v>0.05822436719999999</v>
       </c>
       <c r="P43">
-        <v>0.1432124244</v>
+        <v>0.1425493128</v>
       </c>
       <c r="Q43">
-        <v>0.2072124244</v>
+        <v>0.2065493128</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.264818467288963</v>
+        <v>0.2678613547410735</v>
       </c>
       <c r="T43">
-        <v>1.33948968148642</v>
+        <v>1.358099602350531</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.267568778732885</v>
+        <v>6.118340950667816</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1715518457498227</v>
+        <v>0.1713593657991571</v>
       </c>
       <c r="C44">
-        <v>1.252301256706359</v>
+        <v>1.237840233345466</v>
       </c>
       <c r="D44">
-        <v>1.786701256706359</v>
+        <v>1.789440233345466</v>
       </c>
       <c r="E44">
-        <v>0.7223999999999999</v>
+        <v>0.7395999999999999</v>
       </c>
       <c r="F44">
-        <v>0.7223999999999999</v>
+        <v>0.7395999999999999</v>
       </c>
       <c r="G44">
         <v>0.188</v>
@@ -4895,45 +4895,45 @@
         <v>0.24</v>
       </c>
       <c r="M44">
-        <v>0.03922632</v>
+        <v>0.04089988</v>
       </c>
       <c r="N44">
-        <v>0.20077368</v>
+        <v>0.19910012</v>
       </c>
       <c r="O44">
-        <v>0.0582243672</v>
+        <v>0.05773903479999999</v>
       </c>
       <c r="P44">
-        <v>0.1425493128</v>
+        <v>0.1413610852</v>
       </c>
       <c r="Q44">
-        <v>0.2065493128</v>
+        <v>0.2053610852</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2678613547410735</v>
+        <v>0.2710110101739598</v>
       </c>
       <c r="T44">
-        <v>1.358099602350531</v>
+        <v>1.377362502894085</v>
       </c>
       <c r="U44">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V44">
         <v>0.29</v>
       </c>
       <c r="W44">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y44">
-        <v>6.118340950667818</v>
+        <v>5.867987876737047</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1713593657991571</v>
+        <v>0.1708686858484915</v>
       </c>
       <c r="C45">
-        <v>1.237840233345466</v>
+        <v>1.227660715246751</v>
       </c>
       <c r="D45">
-        <v>1.789440233345466</v>
+        <v>1.796460715246752</v>
       </c>
       <c r="E45">
-        <v>0.7395999999999999</v>
+        <v>0.7568</v>
       </c>
       <c r="F45">
-        <v>0.7395999999999999</v>
+        <v>0.7568</v>
       </c>
       <c r="G45">
         <v>0.188</v>
@@ -4977,28 +4977,28 @@
         <v>0.24</v>
       </c>
       <c r="M45">
-        <v>0.04089988</v>
+        <v>0.04185104000000001</v>
       </c>
       <c r="N45">
-        <v>0.19910012</v>
+        <v>0.19814896</v>
       </c>
       <c r="O45">
-        <v>0.05773903479999999</v>
+        <v>0.05746319839999999</v>
       </c>
       <c r="P45">
-        <v>0.1413610852</v>
+        <v>0.1406857616</v>
       </c>
       <c r="Q45">
-        <v>0.2053610852</v>
+        <v>0.2046857616</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2710110101739598</v>
+        <v>0.2742731533008778</v>
       </c>
       <c r="T45">
-        <v>1.377362502894085</v>
+        <v>1.397313364171336</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.867987876737047</v>
+        <v>5.734624515902112</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1708686858484915</v>
+        <v>0.170378005897826</v>
       </c>
       <c r="C46">
-        <v>1.227660715246751</v>
+        <v>1.217536500805984</v>
       </c>
       <c r="D46">
-        <v>1.796460715246752</v>
+        <v>1.803536500805984</v>
       </c>
       <c r="E46">
-        <v>0.7568</v>
+        <v>0.774</v>
       </c>
       <c r="F46">
-        <v>0.7568</v>
+        <v>0.774</v>
       </c>
       <c r="G46">
         <v>0.188</v>
@@ -5059,28 +5059,28 @@
         <v>0.24</v>
       </c>
       <c r="M46">
-        <v>0.04185104000000001</v>
+        <v>0.04280220000000001</v>
       </c>
       <c r="N46">
-        <v>0.19814896</v>
+        <v>0.1971978</v>
       </c>
       <c r="O46">
-        <v>0.05746319839999999</v>
+        <v>0.05718736199999999</v>
       </c>
       <c r="P46">
-        <v>0.1406857616</v>
+        <v>0.140010438</v>
       </c>
       <c r="Q46">
-        <v>0.2046857616</v>
+        <v>0.204010438</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2742731533008778</v>
+        <v>0.2776539198142291</v>
       </c>
       <c r="T46">
-        <v>1.397313364171336</v>
+        <v>1.417989711313216</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.734624515902112</v>
+        <v>5.607188415548732</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.170378005897826</v>
+        <v>0.1698873259471604</v>
       </c>
       <c r="C47">
-        <v>1.217536500805984</v>
+        <v>1.207468246086851</v>
       </c>
       <c r="D47">
-        <v>1.803536500805984</v>
+        <v>1.810668246086851</v>
       </c>
       <c r="E47">
-        <v>0.774</v>
+        <v>0.7912</v>
       </c>
       <c r="F47">
-        <v>0.774</v>
+        <v>0.7912</v>
       </c>
       <c r="G47">
         <v>0.188</v>
@@ -5141,28 +5141,28 @@
         <v>0.24</v>
       </c>
       <c r="M47">
-        <v>0.04280220000000001</v>
+        <v>0.04375336000000001</v>
       </c>
       <c r="N47">
-        <v>0.1971978</v>
+        <v>0.19624664</v>
       </c>
       <c r="O47">
-        <v>0.05718736199999999</v>
+        <v>0.05691152559999998</v>
       </c>
       <c r="P47">
-        <v>0.140010438</v>
+        <v>0.1393351144</v>
       </c>
       <c r="Q47">
-        <v>0.204010438</v>
+        <v>0.2033351144</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2776539198142291</v>
+        <v>0.281159899902149</v>
       </c>
       <c r="T47">
-        <v>1.417989711313216</v>
+        <v>1.439431849089979</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.607188415548732</v>
+        <v>5.485293015210717</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1698873259471604</v>
+        <v>0.1693966459964949</v>
       </c>
       <c r="C48">
-        <v>1.207468246086851</v>
+        <v>1.197456617571355</v>
       </c>
       <c r="D48">
-        <v>1.810668246086851</v>
+        <v>1.817856617571355</v>
       </c>
       <c r="E48">
-        <v>0.7912</v>
+        <v>0.8084</v>
       </c>
       <c r="F48">
-        <v>0.7912</v>
+        <v>0.8084</v>
       </c>
       <c r="G48">
         <v>0.188</v>
@@ -5223,28 +5223,28 @@
         <v>0.24</v>
       </c>
       <c r="M48">
-        <v>0.04375336000000001</v>
+        <v>0.04470452</v>
       </c>
       <c r="N48">
-        <v>0.19624664</v>
+        <v>0.19529548</v>
       </c>
       <c r="O48">
-        <v>0.05691152559999998</v>
+        <v>0.05663568919999999</v>
       </c>
       <c r="P48">
-        <v>0.1393351144</v>
+        <v>0.1386597908</v>
       </c>
       <c r="Q48">
-        <v>0.2033351144</v>
+        <v>0.2026597908</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.281159899902149</v>
+        <v>0.2847981811254621</v>
       </c>
       <c r="T48">
-        <v>1.439431849089979</v>
+        <v>1.461683124141338</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.485293015210717</v>
+        <v>5.368584653184957</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1693966459964949</v>
+        <v>0.1689059660458294</v>
       </c>
       <c r="C49">
-        <v>1.197456617571355</v>
+        <v>1.187502292367448</v>
       </c>
       <c r="D49">
-        <v>1.817856617571355</v>
+        <v>1.825102292367448</v>
       </c>
       <c r="E49">
-        <v>0.8084</v>
+        <v>0.8256</v>
       </c>
       <c r="F49">
-        <v>0.8084</v>
+        <v>0.8256</v>
       </c>
       <c r="G49">
         <v>0.188</v>
@@ -5305,28 +5305,28 @@
         <v>0.24</v>
       </c>
       <c r="M49">
-        <v>0.04470452</v>
+        <v>0.04565568</v>
       </c>
       <c r="N49">
-        <v>0.19529548</v>
+        <v>0.19434432</v>
       </c>
       <c r="O49">
-        <v>0.05663568919999999</v>
+        <v>0.05635985279999999</v>
       </c>
       <c r="P49">
-        <v>0.1386597908</v>
+        <v>0.1379844672</v>
       </c>
       <c r="Q49">
-        <v>0.2026597908</v>
+        <v>0.2019844672</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2847981811254621</v>
+        <v>0.2885763962419795</v>
       </c>
       <c r="T49">
-        <v>1.461683124141338</v>
+        <v>1.484790217463902</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.368584653184957</v>
+        <v>5.256739139576937</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1689059660458294</v>
+        <v>0.1684152860951638</v>
       </c>
       <c r="C50">
-        <v>1.187502292367448</v>
+        <v>1.177605958421642</v>
       </c>
       <c r="D50">
-        <v>1.825102292367448</v>
+        <v>1.832405958421642</v>
       </c>
       <c r="E50">
-        <v>0.8256</v>
+        <v>0.8428</v>
       </c>
       <c r="F50">
-        <v>0.8256</v>
+        <v>0.8428</v>
       </c>
       <c r="G50">
         <v>0.188</v>
@@ -5387,28 +5387,28 @@
         <v>0.24</v>
       </c>
       <c r="M50">
-        <v>0.04565568</v>
+        <v>0.04660684</v>
       </c>
       <c r="N50">
-        <v>0.19434432</v>
+        <v>0.19339316</v>
       </c>
       <c r="O50">
-        <v>0.05635985279999999</v>
+        <v>0.05608401639999999</v>
       </c>
       <c r="P50">
-        <v>0.1379844672</v>
+        <v>0.1373091436</v>
       </c>
       <c r="Q50">
-        <v>0.2019844672</v>
+        <v>0.2013091436</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2885763962419795</v>
+        <v>0.2925027766571839</v>
       </c>
       <c r="T50">
-        <v>1.484790217463902</v>
+        <v>1.50880347130892</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.256739139576937</v>
+        <v>5.149458748973326</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1684152860951638</v>
+        <v>0.1679246061444983</v>
       </c>
       <c r="C51">
-        <v>1.177605958421642</v>
+        <v>1.167768314736747</v>
       </c>
       <c r="D51">
-        <v>1.832405958421642</v>
+        <v>1.839768314736746</v>
       </c>
       <c r="E51">
-        <v>0.8428</v>
+        <v>0.86</v>
       </c>
       <c r="F51">
-        <v>0.8428</v>
+        <v>0.86</v>
       </c>
       <c r="G51">
         <v>0.188</v>
@@ -5469,28 +5469,28 @@
         <v>0.24</v>
       </c>
       <c r="M51">
-        <v>0.04660684</v>
+        <v>0.047558</v>
       </c>
       <c r="N51">
-        <v>0.19339316</v>
+        <v>0.192442</v>
       </c>
       <c r="O51">
-        <v>0.05608401639999999</v>
+        <v>0.05580818</v>
       </c>
       <c r="P51">
-        <v>0.1373091436</v>
+        <v>0.13663382</v>
       </c>
       <c r="Q51">
-        <v>0.2013091436</v>
+        <v>0.20063382</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2925027766571839</v>
+        <v>0.2965862122889965</v>
       </c>
       <c r="T51">
-        <v>1.50880347130892</v>
+        <v>1.533777255307739</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.149458748973326</v>
+        <v>5.04646957399386</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1679246061444983</v>
+        <v>0.1674339261938327</v>
       </c>
       <c r="C52">
-        <v>1.167768314736747</v>
+        <v>1.157990071594882</v>
       </c>
       <c r="D52">
-        <v>1.839768314736746</v>
+        <v>1.847190071594881</v>
       </c>
       <c r="E52">
-        <v>0.86</v>
+        <v>0.8772</v>
       </c>
       <c r="F52">
-        <v>0.86</v>
+        <v>0.8772</v>
       </c>
       <c r="G52">
         <v>0.188</v>
@@ -5551,28 +5551,28 @@
         <v>0.24</v>
       </c>
       <c r="M52">
-        <v>0.047558</v>
+        <v>0.04850916</v>
       </c>
       <c r="N52">
-        <v>0.192442</v>
+        <v>0.19149084</v>
       </c>
       <c r="O52">
-        <v>0.05580818</v>
+        <v>0.05553234359999999</v>
       </c>
       <c r="P52">
-        <v>0.13663382</v>
+        <v>0.1359584964</v>
       </c>
       <c r="Q52">
-        <v>0.20063382</v>
+        <v>0.1999584964</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2965862122889965</v>
+        <v>0.3008363187629239</v>
       </c>
       <c r="T52">
-        <v>1.533777255307739</v>
+        <v>1.559770377428959</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.04646957399386</v>
+        <v>4.947519190190059</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1674339261938327</v>
+        <v>0.1669432462431672</v>
       </c>
       <c r="C53">
-        <v>1.157990071594882</v>
+        <v>1.148271950785908</v>
       </c>
       <c r="D53">
-        <v>1.847190071594881</v>
+        <v>1.854671950785908</v>
       </c>
       <c r="E53">
-        <v>0.8772</v>
+        <v>0.8944</v>
       </c>
       <c r="F53">
-        <v>0.8772</v>
+        <v>0.8944</v>
       </c>
       <c r="G53">
         <v>0.188</v>
@@ -5633,28 +5633,28 @@
         <v>0.24</v>
       </c>
       <c r="M53">
-        <v>0.04850916</v>
+        <v>0.04946032</v>
       </c>
       <c r="N53">
-        <v>0.19149084</v>
+        <v>0.19053968</v>
       </c>
       <c r="O53">
-        <v>0.05553234359999999</v>
+        <v>0.05525650719999999</v>
       </c>
       <c r="P53">
-        <v>0.1359584964</v>
+        <v>0.1352831728</v>
       </c>
       <c r="Q53">
-        <v>0.1999584964</v>
+        <v>0.1992831728</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3008363187629239</v>
+        <v>0.3052635130065983</v>
       </c>
       <c r="T53">
-        <v>1.559770377428959</v>
+        <v>1.586846546305229</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.947519190190059</v>
+        <v>4.852374590378711</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1669432462431672</v>
+        <v>0.1664525662925016</v>
       </c>
       <c r="C54">
-        <v>1.148271950785908</v>
+        <v>1.138614685841424</v>
       </c>
       <c r="D54">
-        <v>1.854671950785908</v>
+        <v>1.862214685841423</v>
       </c>
       <c r="E54">
-        <v>0.8944</v>
+        <v>0.9116000000000001</v>
       </c>
       <c r="F54">
-        <v>0.8944</v>
+        <v>0.9116000000000001</v>
       </c>
       <c r="G54">
         <v>0.188</v>
@@ -5715,28 +5715,28 @@
         <v>0.24</v>
       </c>
       <c r="M54">
-        <v>0.04946032</v>
+        <v>0.05041148000000001</v>
       </c>
       <c r="N54">
-        <v>0.19053968</v>
+        <v>0.18958852</v>
       </c>
       <c r="O54">
-        <v>0.05525650719999999</v>
+        <v>0.05498067079999999</v>
       </c>
       <c r="P54">
-        <v>0.1352831728</v>
+        <v>0.1346078492</v>
       </c>
       <c r="Q54">
-        <v>0.1992831728</v>
+        <v>0.1986078492</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.3052635130065983</v>
+        <v>0.3098790984946843</v>
       </c>
       <c r="T54">
-        <v>1.586846546305229</v>
+        <v>1.61507489258049</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.852374590378711</v>
+        <v>4.760820352824395</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1664525662925016</v>
+        <v>0.1659618863418361</v>
       </c>
       <c r="C55">
-        <v>1.138614685841424</v>
+        <v>1.129019022274508</v>
       </c>
       <c r="D55">
-        <v>1.862214685841423</v>
+        <v>1.869819022274508</v>
       </c>
       <c r="E55">
-        <v>0.9116000000000001</v>
+        <v>0.9288000000000001</v>
       </c>
       <c r="F55">
-        <v>0.9116000000000001</v>
+        <v>0.9288000000000001</v>
       </c>
       <c r="G55">
         <v>0.188</v>
@@ -5797,28 +5797,28 @@
         <v>0.24</v>
       </c>
       <c r="M55">
-        <v>0.05041148000000001</v>
+        <v>0.05136264000000001</v>
       </c>
       <c r="N55">
-        <v>0.18958852</v>
+        <v>0.18863736</v>
       </c>
       <c r="O55">
-        <v>0.05498067079999999</v>
+        <v>0.05470483439999999</v>
       </c>
       <c r="P55">
-        <v>0.1346078492</v>
+        <v>0.1339325256</v>
       </c>
       <c r="Q55">
-        <v>0.1986078492</v>
+        <v>0.1979325256</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3098790984946843</v>
+        <v>0.3146953616126871</v>
       </c>
       <c r="T55">
-        <v>1.61507489258049</v>
+        <v>1.644530558259023</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.760820352824395</v>
+        <v>4.672657012957277</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1659618863418361</v>
+        <v>0.1654712063911705</v>
       </c>
       <c r="C56">
-        <v>1.129019022274508</v>
+        <v>1.11948571782535</v>
       </c>
       <c r="D56">
-        <v>1.869819022274508</v>
+        <v>1.877485717825351</v>
       </c>
       <c r="E56">
-        <v>0.9288000000000001</v>
+        <v>0.9460000000000001</v>
       </c>
       <c r="F56">
-        <v>0.9288000000000001</v>
+        <v>0.9460000000000001</v>
       </c>
       <c r="G56">
         <v>0.188</v>
@@ -5879,28 +5879,28 @@
         <v>0.24</v>
       </c>
       <c r="M56">
-        <v>0.05136264000000001</v>
+        <v>0.05231380000000001</v>
       </c>
       <c r="N56">
-        <v>0.18863736</v>
+        <v>0.1876862</v>
       </c>
       <c r="O56">
-        <v>0.05470483439999999</v>
+        <v>0.05442899799999999</v>
       </c>
       <c r="P56">
-        <v>0.1339325256</v>
+        <v>0.133257202</v>
       </c>
       <c r="Q56">
-        <v>0.1979325256</v>
+        <v>0.197257202</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3146953616126871</v>
+        <v>0.3197256808692678</v>
       </c>
       <c r="T56">
-        <v>1.644530558259023</v>
+        <v>1.67529536463438</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.672657012957277</v>
+        <v>4.58769961272169</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1654712063911705</v>
+        <v>0.164980526440505</v>
       </c>
       <c r="C57">
-        <v>1.11948571782535</v>
+        <v>1.110015542712957</v>
       </c>
       <c r="D57">
-        <v>1.877485717825351</v>
+        <v>1.885215542712957</v>
       </c>
       <c r="E57">
-        <v>0.9460000000000001</v>
+        <v>0.9632000000000001</v>
       </c>
       <c r="F57">
-        <v>0.9460000000000001</v>
+        <v>0.9632000000000001</v>
       </c>
       <c r="G57">
         <v>0.188</v>
@@ -5961,28 +5961,28 @@
         <v>0.24</v>
       </c>
       <c r="M57">
-        <v>0.05231380000000001</v>
+        <v>0.05326496000000001</v>
       </c>
       <c r="N57">
-        <v>0.1876862</v>
+        <v>0.18673504</v>
       </c>
       <c r="O57">
-        <v>0.05442899799999999</v>
+        <v>0.05415316159999999</v>
       </c>
       <c r="P57">
-        <v>0.133257202</v>
+        <v>0.1325818784</v>
       </c>
       <c r="Q57">
-        <v>0.197257202</v>
+        <v>0.1965818784</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3197256808692678</v>
+        <v>0.3249846510011477</v>
       </c>
       <c r="T57">
-        <v>1.67529536463438</v>
+        <v>1.707458571299525</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.58769961272169</v>
+        <v>4.505776405351661</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.164980526440505</v>
+        <v>0.1655015964898394</v>
       </c>
       <c r="C58">
-        <v>1.110015542712957</v>
+        <v>1.084609057714815</v>
       </c>
       <c r="D58">
-        <v>1.885215542712957</v>
+        <v>1.877009057714815</v>
       </c>
       <c r="E58">
-        <v>0.9632000000000001</v>
+        <v>0.9804</v>
       </c>
       <c r="F58">
-        <v>0.9632000000000001</v>
+        <v>0.9804</v>
       </c>
       <c r="G58">
         <v>0.188</v>
@@ -6043,45 +6043,45 @@
         <v>0.24</v>
       </c>
       <c r="M58">
-        <v>0.05326496000000001</v>
+        <v>0.05666712000000001</v>
       </c>
       <c r="N58">
-        <v>0.18673504</v>
+        <v>0.18333288</v>
       </c>
       <c r="O58">
-        <v>0.05415316159999999</v>
+        <v>0.05316653519999999</v>
       </c>
       <c r="P58">
-        <v>0.1325818784</v>
+        <v>0.1301663448</v>
       </c>
       <c r="Q58">
-        <v>0.1965818784</v>
+        <v>0.1941663448</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3249846510011477</v>
+        <v>0.3304882243949754</v>
       </c>
       <c r="T58">
-        <v>1.707458571299525</v>
+        <v>1.741117741065375</v>
       </c>
       <c r="U58">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V58">
         <v>0.29</v>
       </c>
       <c r="W58">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>4.505776405351661</v>
+        <v>4.235260235565173</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1655015964898394</v>
+        <v>0.1650286665391739</v>
       </c>
       <c r="C59">
-        <v>1.084609057714815</v>
+        <v>1.074854362831703</v>
       </c>
       <c r="D59">
-        <v>1.877009057714815</v>
+        <v>1.884454362831703</v>
       </c>
       <c r="E59">
-        <v>0.9804</v>
+        <v>0.9976000000000002</v>
       </c>
       <c r="F59">
-        <v>0.9804</v>
+        <v>0.9976000000000002</v>
       </c>
       <c r="G59">
         <v>0.188</v>
@@ -6125,28 +6125,28 @@
         <v>0.24</v>
       </c>
       <c r="M59">
-        <v>0.05666712000000001</v>
+        <v>0.05766128000000002</v>
       </c>
       <c r="N59">
-        <v>0.18333288</v>
+        <v>0.18233872</v>
       </c>
       <c r="O59">
-        <v>0.05316653519999999</v>
+        <v>0.05287822879999999</v>
       </c>
       <c r="P59">
-        <v>0.1301663448</v>
+        <v>0.1294604912</v>
       </c>
       <c r="Q59">
-        <v>0.1941663448</v>
+        <v>0.1934604912</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3304882243949754</v>
+        <v>0.3362538727123188</v>
       </c>
       <c r="T59">
-        <v>1.741117741065375</v>
+        <v>1.776379728439123</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.235260235565173</v>
+        <v>4.162238507365774</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1650286665391738</v>
+        <v>0.1645557365885083</v>
       </c>
       <c r="C60">
-        <v>1.074854362831703</v>
+        <v>1.065158967951821</v>
       </c>
       <c r="D60">
-        <v>1.884454362831703</v>
+        <v>1.89195896795182</v>
       </c>
       <c r="E60">
-        <v>0.9975999999999999</v>
+        <v>1.0148</v>
       </c>
       <c r="F60">
-        <v>0.9975999999999999</v>
+        <v>1.0148</v>
       </c>
       <c r="G60">
         <v>0.188</v>
@@ -6207,28 +6207,28 @@
         <v>0.24</v>
       </c>
       <c r="M60">
-        <v>0.05766128</v>
+        <v>0.05865544</v>
       </c>
       <c r="N60">
-        <v>0.18233872</v>
+        <v>0.18134456</v>
       </c>
       <c r="O60">
-        <v>0.05287822879999999</v>
+        <v>0.0525899224</v>
       </c>
       <c r="P60">
-        <v>0.1294604912</v>
+        <v>0.1287546376</v>
       </c>
       <c r="Q60">
-        <v>0.1934604912</v>
+        <v>0.1927546376</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3362538727123187</v>
+        <v>0.3423007721670934</v>
       </c>
       <c r="T60">
-        <v>1.776379728439122</v>
+        <v>1.81336181275793</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.162238507365775</v>
+        <v>4.091692091986694</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1645557365885083</v>
+        <v>0.1640828066378427</v>
       </c>
       <c r="C61">
-        <v>1.065158967951821</v>
+        <v>1.055523584372484</v>
       </c>
       <c r="D61">
-        <v>1.89195896795182</v>
+        <v>1.899523584372484</v>
       </c>
       <c r="E61">
-        <v>1.0148</v>
+        <v>1.032</v>
       </c>
       <c r="F61">
-        <v>1.0148</v>
+        <v>1.032</v>
       </c>
       <c r="G61">
         <v>0.188</v>
@@ -6289,28 +6289,28 @@
         <v>0.24</v>
       </c>
       <c r="M61">
-        <v>0.05865544</v>
+        <v>0.0596496</v>
       </c>
       <c r="N61">
-        <v>0.18134456</v>
+        <v>0.1803504</v>
       </c>
       <c r="O61">
-        <v>0.0525899224</v>
+        <v>0.052301616</v>
       </c>
       <c r="P61">
-        <v>0.1287546376</v>
+        <v>0.128048784</v>
       </c>
       <c r="Q61">
-        <v>0.1927546376</v>
+        <v>0.192048784</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3423007721670934</v>
+        <v>0.3486500165946068</v>
       </c>
       <c r="T61">
-        <v>1.81336181275793</v>
+        <v>1.852193001292679</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.091692091986694</v>
+        <v>4.023497223786915</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1640828066378427</v>
+        <v>0.1651257266871772</v>
       </c>
       <c r="C62">
-        <v>1.055523584372484</v>
+        <v>1.021721538147203</v>
       </c>
       <c r="D62">
-        <v>1.899523584372484</v>
+        <v>1.882921538147203</v>
       </c>
       <c r="E62">
-        <v>1.032</v>
+        <v>1.0492</v>
       </c>
       <c r="F62">
-        <v>1.032</v>
+        <v>1.0492</v>
       </c>
       <c r="G62">
         <v>0.188</v>
@@ -6371,45 +6371,45 @@
         <v>0.24</v>
       </c>
       <c r="M62">
-        <v>0.0596496</v>
+        <v>0.06431595999999999</v>
       </c>
       <c r="N62">
-        <v>0.1803504</v>
+        <v>0.17568404</v>
       </c>
       <c r="O62">
-        <v>0.052301616</v>
+        <v>0.05094837159999999</v>
       </c>
       <c r="P62">
-        <v>0.128048784</v>
+        <v>0.1247356684</v>
       </c>
       <c r="Q62">
-        <v>0.192048784</v>
+        <v>0.1887356684</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3486500165946068</v>
+        <v>0.3553248633004544</v>
       </c>
       <c r="T62">
-        <v>1.852193001292679</v>
+        <v>1.89301553282921</v>
       </c>
       <c r="U62">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V62">
         <v>0.29</v>
       </c>
       <c r="W62">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.023497223786915</v>
+        <v>3.731577667502747</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1651257266871772</v>
+        <v>0.1646776467365116</v>
       </c>
       <c r="C63">
-        <v>1.021721538147203</v>
+        <v>1.011618746184894</v>
       </c>
       <c r="D63">
-        <v>1.882921538147203</v>
+        <v>1.890018746184894</v>
       </c>
       <c r="E63">
-        <v>1.0492</v>
+        <v>1.0664</v>
       </c>
       <c r="F63">
-        <v>1.0492</v>
+        <v>1.0664</v>
       </c>
       <c r="G63">
         <v>0.188</v>
@@ -6453,28 +6453,28 @@
         <v>0.24</v>
       </c>
       <c r="M63">
-        <v>0.06431595999999999</v>
+        <v>0.06537032</v>
       </c>
       <c r="N63">
-        <v>0.17568404</v>
+        <v>0.17462968</v>
       </c>
       <c r="O63">
-        <v>0.05094837159999999</v>
+        <v>0.0506426072</v>
       </c>
       <c r="P63">
-        <v>0.1247356684</v>
+        <v>0.1239870728</v>
       </c>
       <c r="Q63">
-        <v>0.1887356684</v>
+        <v>0.1879870728</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3553248633004544</v>
+        <v>0.3623510177276622</v>
       </c>
       <c r="T63">
-        <v>1.89301553282921</v>
+        <v>1.935986618657137</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.731577667502747</v>
+        <v>3.671390930930123</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1646776467365116</v>
+        <v>0.1642295667858461</v>
       </c>
       <c r="C64">
-        <v>1.011618746184894</v>
+        <v>1.00156965899773</v>
       </c>
       <c r="D64">
-        <v>1.890018746184894</v>
+        <v>1.89716965899773</v>
       </c>
       <c r="E64">
-        <v>1.0664</v>
+        <v>1.0836</v>
       </c>
       <c r="F64">
-        <v>1.0664</v>
+        <v>1.0836</v>
       </c>
       <c r="G64">
         <v>0.188</v>
@@ -6535,28 +6535,28 @@
         <v>0.24</v>
       </c>
       <c r="M64">
-        <v>0.06537032</v>
+        <v>0.06642468</v>
       </c>
       <c r="N64">
-        <v>0.17462968</v>
+        <v>0.17357532</v>
       </c>
       <c r="O64">
-        <v>0.0506426072</v>
+        <v>0.05033684279999999</v>
       </c>
       <c r="P64">
-        <v>0.1239870728</v>
+        <v>0.1232384772</v>
       </c>
       <c r="Q64">
-        <v>0.1879870728</v>
+        <v>0.1872384772</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3623510177276622</v>
+        <v>0.3697569642860705</v>
       </c>
       <c r="T64">
-        <v>1.935986618657137</v>
+        <v>1.981280465881168</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.671390930930123</v>
+        <v>3.613114884407422</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1642295667858461</v>
+        <v>0.1637814868351806</v>
       </c>
       <c r="C65">
-        <v>1.00156965899773</v>
+        <v>0.9915748884791595</v>
       </c>
       <c r="D65">
-        <v>1.89716965899773</v>
+        <v>1.904374888479159</v>
       </c>
       <c r="E65">
-        <v>1.0836</v>
+        <v>1.1008</v>
       </c>
       <c r="F65">
-        <v>1.0836</v>
+        <v>1.1008</v>
       </c>
       <c r="G65">
         <v>0.188</v>
@@ -6617,28 +6617,28 @@
         <v>0.24</v>
       </c>
       <c r="M65">
-        <v>0.06642468</v>
+        <v>0.06747904</v>
       </c>
       <c r="N65">
-        <v>0.17357532</v>
+        <v>0.17252096</v>
       </c>
       <c r="O65">
-        <v>0.05033684279999999</v>
+        <v>0.0500310784</v>
       </c>
       <c r="P65">
-        <v>0.1232384772</v>
+        <v>0.1224898816</v>
       </c>
       <c r="Q65">
-        <v>0.1872384772</v>
+        <v>0.1864898816</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3697569642860705</v>
+        <v>0.3775743523199461</v>
       </c>
       <c r="T65">
-        <v>1.981280465881168</v>
+        <v>2.02909063795098</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.613114884407422</v>
+        <v>3.556659964338556</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1637814868351806</v>
+        <v>0.163333406884515</v>
       </c>
       <c r="C66">
-        <v>0.9915748884791595</v>
+        <v>0.9816350558536737</v>
       </c>
       <c r="D66">
-        <v>1.904374888479159</v>
+        <v>1.911635055853674</v>
       </c>
       <c r="E66">
-        <v>1.1008</v>
+        <v>1.118</v>
       </c>
       <c r="F66">
-        <v>1.1008</v>
+        <v>1.118</v>
       </c>
       <c r="G66">
         <v>0.188</v>
@@ -6699,28 +6699,28 @@
         <v>0.24</v>
       </c>
       <c r="M66">
-        <v>0.06747904</v>
+        <v>0.06853340000000001</v>
       </c>
       <c r="N66">
-        <v>0.17252096</v>
+        <v>0.1714666</v>
       </c>
       <c r="O66">
-        <v>0.0500310784</v>
+        <v>0.04972531399999999</v>
       </c>
       <c r="P66">
-        <v>0.1224898816</v>
+        <v>0.121741286</v>
       </c>
       <c r="Q66">
-        <v>0.1864898816</v>
+        <v>0.185741286</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3775743523199461</v>
+        <v>0.3858384482414715</v>
       </c>
       <c r="T66">
-        <v>2.02909063795098</v>
+        <v>2.079632819853351</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.556659964338556</v>
+        <v>3.501942118733347</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.163333406884515</v>
+        <v>0.1641974069338494</v>
       </c>
       <c r="C67">
-        <v>0.9816350558536737</v>
+        <v>0.9504849802114788</v>
       </c>
       <c r="D67">
-        <v>1.911635055853674</v>
+        <v>1.897684980211479</v>
       </c>
       <c r="E67">
-        <v>1.118</v>
+        <v>1.1352</v>
       </c>
       <c r="F67">
-        <v>1.118</v>
+        <v>1.1352</v>
       </c>
       <c r="G67">
         <v>0.188</v>
@@ -6781,45 +6781,45 @@
         <v>0.24</v>
       </c>
       <c r="M67">
-        <v>0.06853340000000001</v>
+        <v>0.07276632000000001</v>
       </c>
       <c r="N67">
-        <v>0.1714666</v>
+        <v>0.16723368</v>
       </c>
       <c r="O67">
-        <v>0.04972531399999999</v>
+        <v>0.04849776719999999</v>
       </c>
       <c r="P67">
-        <v>0.121741286</v>
+        <v>0.1187359128</v>
       </c>
       <c r="Q67">
-        <v>0.185741286</v>
+        <v>0.1827359128</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3858384482414715</v>
+        <v>0.3945886674524984</v>
       </c>
       <c r="T67">
-        <v>2.079632819853351</v>
+        <v>2.133148071279391</v>
       </c>
       <c r="U67">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V67">
         <v>0.29</v>
       </c>
       <c r="W67">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y67">
-        <v>3.501942118733347</v>
+        <v>3.298229180752854</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1641974069338494</v>
+        <v>0.1637692069831839</v>
       </c>
       <c r="C68">
-        <v>0.9504849802114788</v>
+        <v>0.9401731219196887</v>
       </c>
       <c r="D68">
-        <v>1.897684980211479</v>
+        <v>1.904573121919689</v>
       </c>
       <c r="E68">
-        <v>1.1352</v>
+        <v>1.1524</v>
       </c>
       <c r="F68">
-        <v>1.1352</v>
+        <v>1.1524</v>
       </c>
       <c r="G68">
         <v>0.188</v>
@@ -6863,28 +6863,28 @@
         <v>0.24</v>
       </c>
       <c r="M68">
-        <v>0.07276632000000001</v>
+        <v>0.07386884000000001</v>
       </c>
       <c r="N68">
-        <v>0.16723368</v>
+        <v>0.16613116</v>
       </c>
       <c r="O68">
-        <v>0.04849776719999999</v>
+        <v>0.0481780364</v>
       </c>
       <c r="P68">
-        <v>0.1187359128</v>
+        <v>0.1179531236</v>
       </c>
       <c r="Q68">
-        <v>0.1827359128</v>
+        <v>0.1819531236</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3945886674524984</v>
+        <v>0.4038692029793451</v>
       </c>
       <c r="T68">
-        <v>2.133148071279391</v>
+        <v>2.189906671276706</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.298229180752854</v>
+        <v>3.249001879547587</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1637692069831839</v>
+        <v>0.1633410070325183</v>
       </c>
       <c r="C69">
-        <v>0.9401731219196887</v>
+        <v>0.929911450401248</v>
       </c>
       <c r="D69">
-        <v>1.904573121919689</v>
+        <v>1.911511450401248</v>
       </c>
       <c r="E69">
-        <v>1.1524</v>
+        <v>1.1696</v>
       </c>
       <c r="F69">
-        <v>1.1524</v>
+        <v>1.1696</v>
       </c>
       <c r="G69">
         <v>0.188</v>
@@ -6945,28 +6945,28 @@
         <v>0.24</v>
       </c>
       <c r="M69">
-        <v>0.07386884000000001</v>
+        <v>0.07497136</v>
       </c>
       <c r="N69">
-        <v>0.16613116</v>
+        <v>0.16502864</v>
       </c>
       <c r="O69">
-        <v>0.0481780364</v>
+        <v>0.0478583056</v>
       </c>
       <c r="P69">
-        <v>0.1179531236</v>
+        <v>0.1171703344</v>
       </c>
       <c r="Q69">
-        <v>0.1819531236</v>
+        <v>0.1811703344</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.4038692029793451</v>
+        <v>0.4137297719766199</v>
       </c>
       <c r="T69">
-        <v>2.189906671276706</v>
+        <v>2.250212683773854</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.249001879547587</v>
+        <v>3.201222440142476</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1633410070325183</v>
+        <v>0.1629128070818529</v>
       </c>
       <c r="C70">
-        <v>0.929911450401248</v>
+        <v>0.9197005161503615</v>
       </c>
       <c r="D70">
-        <v>1.911511450401248</v>
+        <v>1.918500516150362</v>
       </c>
       <c r="E70">
-        <v>1.1696</v>
+        <v>1.1868</v>
       </c>
       <c r="F70">
-        <v>1.1696</v>
+        <v>1.1868</v>
       </c>
       <c r="G70">
         <v>0.188</v>
@@ -7027,28 +7027,28 @@
         <v>0.24</v>
       </c>
       <c r="M70">
-        <v>0.07497136</v>
+        <v>0.07607388000000001</v>
       </c>
       <c r="N70">
-        <v>0.16502864</v>
+        <v>0.16392612</v>
       </c>
       <c r="O70">
-        <v>0.0478583056</v>
+        <v>0.04753857479999999</v>
       </c>
       <c r="P70">
-        <v>0.1171703344</v>
+        <v>0.1163875452</v>
       </c>
       <c r="Q70">
-        <v>0.1811703344</v>
+        <v>0.1803875452</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4137297719766199</v>
+        <v>0.4242265067156544</v>
       </c>
       <c r="T70">
-        <v>2.250212683773854</v>
+        <v>2.31440940675469</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.201222440142476</v>
+        <v>3.154827912024468</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1629128070818529</v>
+        <v>0.1624846071311873</v>
       </c>
       <c r="C71">
-        <v>0.9197005161503615</v>
+        <v>0.9095408777418768</v>
       </c>
       <c r="D71">
-        <v>1.918500516150362</v>
+        <v>1.925540877741877</v>
       </c>
       <c r="E71">
-        <v>1.1868</v>
+        <v>1.204</v>
       </c>
       <c r="F71">
-        <v>1.1868</v>
+        <v>1.204</v>
       </c>
       <c r="G71">
         <v>0.188</v>
@@ -7109,28 +7109,28 @@
         <v>0.24</v>
       </c>
       <c r="M71">
-        <v>0.07607388000000001</v>
+        <v>0.07717640000000002</v>
       </c>
       <c r="N71">
-        <v>0.16392612</v>
+        <v>0.1628236</v>
       </c>
       <c r="O71">
-        <v>0.04753857479999999</v>
+        <v>0.04721884399999998</v>
       </c>
       <c r="P71">
-        <v>0.1163875452</v>
+        <v>0.115604756</v>
       </c>
       <c r="Q71">
-        <v>0.1803875452</v>
+        <v>0.179604756</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4242265067156544</v>
+        <v>0.4354230237706243</v>
       </c>
       <c r="T71">
-        <v>2.31440940675469</v>
+        <v>2.38288591126758</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.154827912024468</v>
+        <v>3.109758941852689</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1624846071311873</v>
+        <v>0.1620564071805217</v>
       </c>
       <c r="C72">
-        <v>0.9095408777418768</v>
+        <v>0.8994331019800925</v>
       </c>
       <c r="D72">
-        <v>1.925540877741877</v>
+        <v>1.932633101980093</v>
       </c>
       <c r="E72">
-        <v>1.204</v>
+        <v>1.2212</v>
       </c>
       <c r="F72">
-        <v>1.204</v>
+        <v>1.2212</v>
       </c>
       <c r="G72">
         <v>0.188</v>
@@ -7191,28 +7191,28 @@
         <v>0.24</v>
       </c>
       <c r="M72">
-        <v>0.07717640000000002</v>
+        <v>0.07827892000000002</v>
       </c>
       <c r="N72">
-        <v>0.1628236</v>
+        <v>0.16172108</v>
       </c>
       <c r="O72">
-        <v>0.04721884399999998</v>
+        <v>0.04689911319999999</v>
       </c>
       <c r="P72">
-        <v>0.115604756</v>
+        <v>0.1148219668</v>
       </c>
       <c r="Q72">
-        <v>0.179604756</v>
+        <v>0.1788219668</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4354230237706243</v>
+        <v>0.4473917144155922</v>
       </c>
       <c r="T72">
-        <v>2.38288591126758</v>
+        <v>2.456084933333083</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.109758941852689</v>
+        <v>3.065959520136455</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1620564071805217</v>
+        <v>0.1616282072298562</v>
       </c>
       <c r="C73">
-        <v>0.8994331019800927</v>
+        <v>0.8893777640508804</v>
       </c>
       <c r="D73">
-        <v>1.932633101980093</v>
+        <v>1.93977776405088</v>
       </c>
       <c r="E73">
-        <v>1.2212</v>
+        <v>1.2384</v>
       </c>
       <c r="F73">
-        <v>1.2212</v>
+        <v>1.2384</v>
       </c>
       <c r="G73">
         <v>0.188</v>
@@ -7273,28 +7273,28 @@
         <v>0.24</v>
       </c>
       <c r="M73">
-        <v>0.07827892</v>
+        <v>0.07938144</v>
       </c>
       <c r="N73">
-        <v>0.16172108</v>
+        <v>0.16061856</v>
       </c>
       <c r="O73">
-        <v>0.04689911319999999</v>
+        <v>0.04657938239999999</v>
       </c>
       <c r="P73">
-        <v>0.1148219668</v>
+        <v>0.1140391776</v>
       </c>
       <c r="Q73">
-        <v>0.1788219668</v>
+        <v>0.1780391776</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4473917144155921</v>
+        <v>0.4602153115352006</v>
       </c>
       <c r="T73">
-        <v>2.456084933333083</v>
+        <v>2.534512456974694</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.065959520136456</v>
+        <v>3.023376749023449</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1616282072298562</v>
+        <v>0.1652427472791906</v>
       </c>
       <c r="C74">
-        <v>0.8893777640508804</v>
+        <v>0.8134767999933346</v>
       </c>
       <c r="D74">
-        <v>1.93977776405088</v>
+        <v>1.881076799993335</v>
       </c>
       <c r="E74">
-        <v>1.2384</v>
+        <v>1.2556</v>
       </c>
       <c r="F74">
-        <v>1.2384</v>
+        <v>1.2556</v>
       </c>
       <c r="G74">
         <v>0.188</v>
@@ -7355,45 +7355,45 @@
         <v>0.24</v>
       </c>
       <c r="M74">
-        <v>0.07938144</v>
+        <v>0.09027764000000001</v>
       </c>
       <c r="N74">
-        <v>0.16061856</v>
+        <v>0.14972236</v>
       </c>
       <c r="O74">
-        <v>0.04657938239999999</v>
+        <v>0.0434194844</v>
       </c>
       <c r="P74">
-        <v>0.1140391776</v>
+        <v>0.1063028756</v>
       </c>
       <c r="Q74">
-        <v>0.1780391776</v>
+        <v>0.1703028756</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4602153115352006</v>
+        <v>0.4739888047377429</v>
       </c>
       <c r="T74">
-        <v>2.534512456974694</v>
+        <v>2.618749426811979</v>
       </c>
       <c r="U74">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.29</v>
       </c>
       <c r="W74">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.023376749023449</v>
+        <v>2.658465595689032</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1652427472791906</v>
+        <v>0.164869927328525</v>
       </c>
       <c r="C75">
-        <v>0.8134767999933346</v>
+        <v>0.8021666411606743</v>
       </c>
       <c r="D75">
-        <v>1.881076799993335</v>
+        <v>1.886966641160674</v>
       </c>
       <c r="E75">
-        <v>1.2556</v>
+        <v>1.2728</v>
       </c>
       <c r="F75">
-        <v>1.2556</v>
+        <v>1.2728</v>
       </c>
       <c r="G75">
         <v>0.188</v>
@@ -7437,28 +7437,28 @@
         <v>0.24</v>
       </c>
       <c r="M75">
-        <v>0.09027764000000001</v>
+        <v>0.09151432</v>
       </c>
       <c r="N75">
-        <v>0.14972236</v>
+        <v>0.14848568</v>
       </c>
       <c r="O75">
-        <v>0.0434194844</v>
+        <v>0.0430608472</v>
       </c>
       <c r="P75">
-        <v>0.1063028756</v>
+        <v>0.1054248328</v>
       </c>
       <c r="Q75">
-        <v>0.1703028756</v>
+        <v>0.1694248328</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4739888047377429</v>
+        <v>0.488821797417404</v>
       </c>
       <c r="T75">
-        <v>2.618749426811979</v>
+        <v>2.709466163559825</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.658465595689032</v>
+        <v>2.622540384936478</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.164869927328525</v>
+        <v>0.1644971073778595</v>
       </c>
       <c r="C76">
-        <v>0.8021666411606743</v>
+        <v>0.790893481549678</v>
       </c>
       <c r="D76">
-        <v>1.886966641160674</v>
+        <v>1.892893481549678</v>
       </c>
       <c r="E76">
-        <v>1.2728</v>
+        <v>1.29</v>
       </c>
       <c r="F76">
-        <v>1.2728</v>
+        <v>1.29</v>
       </c>
       <c r="G76">
         <v>0.188</v>
@@ -7519,28 +7519,28 @@
         <v>0.24</v>
       </c>
       <c r="M76">
-        <v>0.09151432</v>
+        <v>0.09275100000000001</v>
       </c>
       <c r="N76">
-        <v>0.14848568</v>
+        <v>0.147249</v>
       </c>
       <c r="O76">
-        <v>0.0430608472</v>
+        <v>0.04270220999999998</v>
       </c>
       <c r="P76">
-        <v>0.1054248328</v>
+        <v>0.10454679</v>
       </c>
       <c r="Q76">
-        <v>0.1694248328</v>
+        <v>0.16854679</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.488821797417404</v>
+        <v>0.504841429511438</v>
       </c>
       <c r="T76">
-        <v>2.709466163559825</v>
+        <v>2.807440239247499</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.622540384936478</v>
+        <v>2.587573179803991</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1644971073778595</v>
+        <v>0.164124287427194</v>
       </c>
       <c r="C77">
-        <v>0.790893481549678</v>
+        <v>0.7796576708953413</v>
       </c>
       <c r="D77">
-        <v>1.892893481549678</v>
+        <v>1.898857670895341</v>
       </c>
       <c r="E77">
-        <v>1.29</v>
+        <v>1.3072</v>
       </c>
       <c r="F77">
-        <v>1.29</v>
+        <v>1.3072</v>
       </c>
       <c r="G77">
         <v>0.188</v>
@@ -7601,28 +7601,28 @@
         <v>0.24</v>
       </c>
       <c r="M77">
-        <v>0.09275100000000001</v>
+        <v>0.09398768</v>
       </c>
       <c r="N77">
-        <v>0.147249</v>
+        <v>0.14601232</v>
       </c>
       <c r="O77">
-        <v>0.04270220999999998</v>
+        <v>0.04234357279999999</v>
       </c>
       <c r="P77">
-        <v>0.10454679</v>
+        <v>0.1036687472</v>
       </c>
       <c r="Q77">
-        <v>0.16854679</v>
+        <v>0.1676687472</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.504841429511438</v>
+        <v>0.5221960309466415</v>
       </c>
       <c r="T77">
-        <v>2.807440239247499</v>
+        <v>2.91357882124248</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.587573179803991</v>
+        <v>2.553526164280254</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.164124287427194</v>
+        <v>0.1637514674765284</v>
       </c>
       <c r="C78">
-        <v>0.7796576708953413</v>
+        <v>0.7684595633544158</v>
       </c>
       <c r="D78">
-        <v>1.898857670895341</v>
+        <v>1.904859563354416</v>
       </c>
       <c r="E78">
-        <v>1.3072</v>
+        <v>1.3244</v>
       </c>
       <c r="F78">
-        <v>1.3072</v>
+        <v>1.3244</v>
       </c>
       <c r="G78">
         <v>0.188</v>
@@ -7683,28 +7683,28 @@
         <v>0.24</v>
       </c>
       <c r="M78">
-        <v>0.09398768</v>
+        <v>0.09522436000000001</v>
       </c>
       <c r="N78">
-        <v>0.14601232</v>
+        <v>0.14477564</v>
       </c>
       <c r="O78">
-        <v>0.04234357279999999</v>
+        <v>0.0419849356</v>
       </c>
       <c r="P78">
-        <v>0.1036687472</v>
+        <v>0.1027907044</v>
       </c>
       <c r="Q78">
-        <v>0.1676687472</v>
+        <v>0.1667907044</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5221960309466415</v>
+        <v>0.5410597281588191</v>
       </c>
       <c r="T78">
-        <v>2.91357882124248</v>
+        <v>3.028946845150066</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.553526164280254</v>
+        <v>2.520363486822069</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1637514674765284</v>
+        <v>0.1655384675258628</v>
       </c>
       <c r="C79">
-        <v>0.7684595633544158</v>
+        <v>0.7228310707903671</v>
       </c>
       <c r="D79">
-        <v>1.904859563354416</v>
+        <v>1.876431070790367</v>
       </c>
       <c r="E79">
-        <v>1.3244</v>
+        <v>1.3416</v>
       </c>
       <c r="F79">
-        <v>1.3244</v>
+        <v>1.3416</v>
       </c>
       <c r="G79">
         <v>0.188</v>
@@ -7765,45 +7765,45 @@
         <v>0.24</v>
       </c>
       <c r="M79">
-        <v>0.09522436000000001</v>
+        <v>0.10169328</v>
       </c>
       <c r="N79">
-        <v>0.14477564</v>
+        <v>0.13830672</v>
       </c>
       <c r="O79">
-        <v>0.0419849356</v>
+        <v>0.04010894879999999</v>
       </c>
       <c r="P79">
-        <v>0.1027907044</v>
+        <v>0.09819777119999998</v>
       </c>
       <c r="Q79">
-        <v>0.1667907044</v>
+        <v>0.1621977712</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5410597281588191</v>
+        <v>0.5616383069357402</v>
       </c>
       <c r="T79">
-        <v>3.028946845150066</v>
+        <v>3.154802871231071</v>
       </c>
       <c r="U79">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.29</v>
       </c>
       <c r="W79">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.520363486822069</v>
+        <v>2.360037949410226</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1655384675258628</v>
+        <v>0.1651933375751973</v>
       </c>
       <c r="C80">
-        <v>0.7228310707903671</v>
+        <v>0.7110552642675056</v>
       </c>
       <c r="D80">
-        <v>1.876431070790367</v>
+        <v>1.881855264267506</v>
       </c>
       <c r="E80">
-        <v>1.3416</v>
+        <v>1.3588</v>
       </c>
       <c r="F80">
-        <v>1.3416</v>
+        <v>1.3588</v>
       </c>
       <c r="G80">
         <v>0.188</v>
@@ -7847,28 +7847,28 @@
         <v>0.24</v>
       </c>
       <c r="M80">
-        <v>0.10169328</v>
+        <v>0.10299704</v>
       </c>
       <c r="N80">
-        <v>0.13830672</v>
+        <v>0.13700296</v>
       </c>
       <c r="O80">
-        <v>0.04010894879999999</v>
+        <v>0.03973085839999999</v>
       </c>
       <c r="P80">
-        <v>0.09819777119999998</v>
+        <v>0.09727210159999999</v>
       </c>
       <c r="Q80">
-        <v>0.1621977712</v>
+        <v>0.1612721016</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5616383069357402</v>
+        <v>0.5841767503580825</v>
       </c>
       <c r="T80">
-        <v>3.154802871231071</v>
+        <v>3.292645185510266</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.360037949410226</v>
+        <v>2.330164051316426</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1651933375751973</v>
+        <v>0.1648482076245317</v>
       </c>
       <c r="C81">
-        <v>0.7110552642675056</v>
+        <v>0.6993109080564894</v>
       </c>
       <c r="D81">
-        <v>1.881855264267506</v>
+        <v>1.887310908056489</v>
       </c>
       <c r="E81">
-        <v>1.3588</v>
+        <v>1.376</v>
       </c>
       <c r="F81">
-        <v>1.3588</v>
+        <v>1.376</v>
       </c>
       <c r="G81">
         <v>0.188</v>
@@ -7929,28 +7929,28 @@
         <v>0.24</v>
       </c>
       <c r="M81">
-        <v>0.10299704</v>
+        <v>0.1043008</v>
       </c>
       <c r="N81">
-        <v>0.13700296</v>
+        <v>0.1356992</v>
       </c>
       <c r="O81">
-        <v>0.03973085839999999</v>
+        <v>0.03935276799999999</v>
       </c>
       <c r="P81">
-        <v>0.09727210159999999</v>
+        <v>0.09634643199999998</v>
       </c>
       <c r="Q81">
-        <v>0.1612721016</v>
+        <v>0.160346432</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5841767503580825</v>
+        <v>0.6089690381226588</v>
       </c>
       <c r="T81">
-        <v>3.292645185510266</v>
+        <v>3.44427173121738</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.330164051316426</v>
+        <v>2.30103700067497</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1648482076245317</v>
+        <v>0.1645030776738662</v>
       </c>
       <c r="C82">
-        <v>0.6993109080564894</v>
+        <v>0.68759827648326</v>
       </c>
       <c r="D82">
-        <v>1.887310908056489</v>
+        <v>1.89279827648326</v>
       </c>
       <c r="E82">
-        <v>1.376</v>
+        <v>1.3932</v>
       </c>
       <c r="F82">
-        <v>1.376</v>
+        <v>1.3932</v>
       </c>
       <c r="G82">
         <v>0.188</v>
@@ -8011,28 +8011,28 @@
         <v>0.24</v>
       </c>
       <c r="M82">
-        <v>0.1043008</v>
+        <v>0.10560456</v>
       </c>
       <c r="N82">
-        <v>0.1356992</v>
+        <v>0.13439544</v>
       </c>
       <c r="O82">
-        <v>0.03935276799999999</v>
+        <v>0.03897467759999999</v>
       </c>
       <c r="P82">
-        <v>0.09634643199999998</v>
+        <v>0.09542076239999998</v>
       </c>
       <c r="Q82">
-        <v>0.160346432</v>
+        <v>0.1594207624</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.6089690381226588</v>
+        <v>0.6363710403887696</v>
       </c>
       <c r="T82">
-        <v>3.44427173121738</v>
+        <v>3.611858965946296</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.30103700067497</v>
+        <v>2.272629136469106</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1645030776738662</v>
+        <v>0.1641579477232006</v>
       </c>
       <c r="C83">
-        <v>0.68759827648326</v>
+        <v>0.675917647073482</v>
       </c>
       <c r="D83">
-        <v>1.89279827648326</v>
+        <v>1.898317647073482</v>
       </c>
       <c r="E83">
-        <v>1.3932</v>
+        <v>1.4104</v>
       </c>
       <c r="F83">
-        <v>1.3932</v>
+        <v>1.4104</v>
       </c>
       <c r="G83">
         <v>0.188</v>
@@ -8093,28 +8093,28 @@
         <v>0.24</v>
       </c>
       <c r="M83">
-        <v>0.10560456</v>
+        <v>0.10690832</v>
       </c>
       <c r="N83">
-        <v>0.13439544</v>
+        <v>0.13309168</v>
       </c>
       <c r="O83">
-        <v>0.03897467759999999</v>
+        <v>0.0385965872</v>
       </c>
       <c r="P83">
-        <v>0.09542076239999998</v>
+        <v>0.09449509279999999</v>
       </c>
       <c r="Q83">
-        <v>0.1594207624</v>
+        <v>0.1584950928</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6363710403887696</v>
+        <v>0.6668177095733371</v>
       </c>
       <c r="T83">
-        <v>3.611858965946296</v>
+        <v>3.79806700453398</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.272629136469106</v>
+        <v>2.244914146999971</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1641579477232006</v>
+        <v>0.1638128177725351</v>
       </c>
       <c r="C84">
-        <v>0.675917647073482</v>
+        <v>0.6642693005993283</v>
       </c>
       <c r="D84">
-        <v>1.898317647073482</v>
+        <v>1.903869300599328</v>
       </c>
       <c r="E84">
-        <v>1.4104</v>
+        <v>1.4276</v>
       </c>
       <c r="F84">
-        <v>1.4104</v>
+        <v>1.4276</v>
       </c>
       <c r="G84">
         <v>0.188</v>
@@ -8175,28 +8175,28 @@
         <v>0.24</v>
       </c>
       <c r="M84">
-        <v>0.10690832</v>
+        <v>0.10821208</v>
       </c>
       <c r="N84">
-        <v>0.13309168</v>
+        <v>0.1317879199999999</v>
       </c>
       <c r="O84">
-        <v>0.0385965872</v>
+        <v>0.03821849679999998</v>
       </c>
       <c r="P84">
-        <v>0.09449509279999999</v>
+        <v>0.09356942319999997</v>
       </c>
       <c r="Q84">
-        <v>0.1584950928</v>
+        <v>0.1575694232</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6668177095733371</v>
+        <v>0.700846339838442</v>
       </c>
       <c r="T84">
-        <v>3.79806700453398</v>
+        <v>4.006181871190805</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.244914146999971</v>
+        <v>2.217866988602381</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1638128177725351</v>
+        <v>0.1634676878218696</v>
       </c>
       <c r="C85">
-        <v>0.6642693005993283</v>
+        <v>0.6526535211270932</v>
       </c>
       <c r="D85">
-        <v>1.903869300599328</v>
+        <v>1.909453521127093</v>
       </c>
       <c r="E85">
-        <v>1.4276</v>
+        <v>1.4448</v>
       </c>
       <c r="F85">
-        <v>1.4276</v>
+        <v>1.4448</v>
       </c>
       <c r="G85">
         <v>0.188</v>
@@ -8257,28 +8257,28 @@
         <v>0.24</v>
       </c>
       <c r="M85">
-        <v>0.10821208</v>
+        <v>0.10951584</v>
       </c>
       <c r="N85">
-        <v>0.1317879199999999</v>
+        <v>0.13048416</v>
       </c>
       <c r="O85">
-        <v>0.03821849679999998</v>
+        <v>0.03784040639999998</v>
       </c>
       <c r="P85">
-        <v>0.09356942319999997</v>
+        <v>0.09264375359999998</v>
       </c>
       <c r="Q85">
-        <v>0.1575694232</v>
+        <v>0.1566437536</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.700846339838442</v>
+        <v>0.7391285488866851</v>
       </c>
       <c r="T85">
-        <v>4.006181871190805</v>
+        <v>4.240311096179732</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.217866988602381</v>
+        <v>2.191463810166638</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1634676878218696</v>
+        <v>0.163122557871204</v>
       </c>
       <c r="C86">
-        <v>0.6526535211270934</v>
+        <v>0.641070596065642</v>
       </c>
       <c r="D86">
-        <v>1.909453521127093</v>
+        <v>1.915070596065642</v>
       </c>
       <c r="E86">
-        <v>1.4448</v>
+        <v>1.462</v>
       </c>
       <c r="F86">
-        <v>1.4448</v>
+        <v>1.462</v>
       </c>
       <c r="G86">
         <v>0.188</v>
@@ -8339,28 +8339,28 @@
         <v>0.24</v>
       </c>
       <c r="M86">
-        <v>0.10951584</v>
+        <v>0.1108196</v>
       </c>
       <c r="N86">
-        <v>0.13048416</v>
+        <v>0.1291804</v>
       </c>
       <c r="O86">
-        <v>0.03784040639999999</v>
+        <v>0.03746231599999999</v>
       </c>
       <c r="P86">
-        <v>0.09264375359999999</v>
+        <v>0.09171808399999998</v>
       </c>
       <c r="Q86">
-        <v>0.1566437536</v>
+        <v>0.155718084</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7391285488866847</v>
+        <v>0.7825150524746932</v>
       </c>
       <c r="T86">
-        <v>4.240311096179729</v>
+        <v>4.505657551167179</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.191463810166639</v>
+        <v>2.165681882988208</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.163122557871204</v>
+        <v>0.1627774279205385</v>
       </c>
       <c r="C87">
-        <v>0.641070596065642</v>
+        <v>0.6295208162157226</v>
       </c>
       <c r="D87">
-        <v>1.915070596065642</v>
+        <v>1.920720816215722</v>
       </c>
       <c r="E87">
-        <v>1.462</v>
+        <v>1.4792</v>
       </c>
       <c r="F87">
-        <v>1.462</v>
+        <v>1.4792</v>
       </c>
       <c r="G87">
         <v>0.188</v>
@@ -8421,28 +8421,28 @@
         <v>0.24</v>
       </c>
       <c r="M87">
-        <v>0.1108196</v>
+        <v>0.11212336</v>
       </c>
       <c r="N87">
-        <v>0.1291804</v>
+        <v>0.12787664</v>
       </c>
       <c r="O87">
-        <v>0.03746231599999999</v>
+        <v>0.03708422559999999</v>
       </c>
       <c r="P87">
-        <v>0.09171808399999998</v>
+        <v>0.09079241439999999</v>
       </c>
       <c r="Q87">
-        <v>0.155718084</v>
+        <v>0.1547924144</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7825150524746932</v>
+        <v>0.8320996280038461</v>
       </c>
       <c r="T87">
-        <v>4.505657551167179</v>
+        <v>4.808910642581408</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.165681882988208</v>
+        <v>2.140499535511601</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1627774279205385</v>
+        <v>0.1624322979698729</v>
       </c>
       <c r="C88">
-        <v>0.6295208162157226</v>
+        <v>0.6180044758201491</v>
       </c>
       <c r="D88">
-        <v>1.920720816215722</v>
+        <v>1.926404475820149</v>
       </c>
       <c r="E88">
-        <v>1.4792</v>
+        <v>1.4964</v>
       </c>
       <c r="F88">
-        <v>1.4792</v>
+        <v>1.4964</v>
       </c>
       <c r="G88">
         <v>0.188</v>
@@ -8503,28 +8503,28 @@
         <v>0.24</v>
       </c>
       <c r="M88">
-        <v>0.11212336</v>
+        <v>0.11342712</v>
       </c>
       <c r="N88">
-        <v>0.12787664</v>
+        <v>0.12657288</v>
       </c>
       <c r="O88">
-        <v>0.03708422559999999</v>
+        <v>0.0367061352</v>
       </c>
       <c r="P88">
-        <v>0.09079241439999999</v>
+        <v>0.08986674480000001</v>
       </c>
       <c r="Q88">
-        <v>0.1547924144</v>
+        <v>0.1538667448</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8320996280038461</v>
+        <v>0.8893125997682529</v>
       </c>
       <c r="T88">
-        <v>4.808910642581408</v>
+        <v>5.158818055751671</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.140499535511601</v>
+        <v>2.115896092574686</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1624322979698729</v>
+        <v>0.1620871680192074</v>
       </c>
       <c r="C89">
-        <v>0.6180044758201491</v>
+        <v>0.6065218726148827</v>
       </c>
       <c r="D89">
-        <v>1.926404475820149</v>
+        <v>1.932121872614883</v>
       </c>
       <c r="E89">
-        <v>1.4964</v>
+        <v>1.5136</v>
       </c>
       <c r="F89">
-        <v>1.4964</v>
+        <v>1.5136</v>
       </c>
       <c r="G89">
         <v>0.188</v>
@@ -8585,28 +8585,28 @@
         <v>0.24</v>
       </c>
       <c r="M89">
-        <v>0.11342712</v>
+        <v>0.11473088</v>
       </c>
       <c r="N89">
-        <v>0.12657288</v>
+        <v>0.12526912</v>
       </c>
       <c r="O89">
-        <v>0.0367061352</v>
+        <v>0.03632804479999999</v>
       </c>
       <c r="P89">
-        <v>0.08986674480000001</v>
+        <v>0.0889410752</v>
       </c>
       <c r="Q89">
-        <v>0.1538667448</v>
+        <v>0.1529410752</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8893125997682529</v>
+        <v>0.956061066826728</v>
       </c>
       <c r="T89">
-        <v>5.158818055751671</v>
+        <v>5.56704337111698</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.115896092574686</v>
+        <v>2.091851818795428</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1620871680192074</v>
+        <v>0.1617420380685418</v>
       </c>
       <c r="C90">
-        <v>0.6065218726148827</v>
+        <v>0.595073307881022</v>
       </c>
       <c r="D90">
-        <v>1.932121872614883</v>
+        <v>1.937873307881022</v>
       </c>
       <c r="E90">
-        <v>1.5136</v>
+        <v>1.5308</v>
       </c>
       <c r="F90">
-        <v>1.5136</v>
+        <v>1.5308</v>
       </c>
       <c r="G90">
         <v>0.188</v>
@@ -8667,28 +8667,28 @@
         <v>0.24</v>
       </c>
       <c r="M90">
-        <v>0.11473088</v>
+        <v>0.11603464</v>
       </c>
       <c r="N90">
-        <v>0.12526912</v>
+        <v>0.12396536</v>
       </c>
       <c r="O90">
-        <v>0.03632804479999999</v>
+        <v>0.03594995439999999</v>
       </c>
       <c r="P90">
-        <v>0.0889410752</v>
+        <v>0.08801540559999999</v>
       </c>
       <c r="Q90">
-        <v>0.1529410752</v>
+        <v>0.1520154056</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.956061066826728</v>
+        <v>1.034945618804926</v>
       </c>
       <c r="T90">
-        <v>5.56704337111698</v>
+        <v>6.049491471094162</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.091851818795428</v>
+        <v>2.068347865775254</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1617420380685418</v>
+        <v>0.1613969081178763</v>
       </c>
       <c r="C91">
-        <v>0.595073307881022</v>
+        <v>0.5836590864977214</v>
       </c>
       <c r="D91">
-        <v>1.937873307881022</v>
+        <v>1.943659086497721</v>
       </c>
       <c r="E91">
-        <v>1.5308</v>
+        <v>1.548</v>
       </c>
       <c r="F91">
-        <v>1.5308</v>
+        <v>1.548</v>
       </c>
       <c r="G91">
         <v>0.188</v>
@@ -8749,28 +8749,28 @@
         <v>0.24</v>
       </c>
       <c r="M91">
-        <v>0.11603464</v>
+        <v>0.1173384</v>
       </c>
       <c r="N91">
-        <v>0.12396536</v>
+        <v>0.1226616</v>
       </c>
       <c r="O91">
-        <v>0.03594995439999999</v>
+        <v>0.03557186399999999</v>
       </c>
       <c r="P91">
-        <v>0.08801540559999999</v>
+        <v>0.08708973599999999</v>
       </c>
       <c r="Q91">
-        <v>0.1520154056</v>
+        <v>0.151089736</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.034945618804926</v>
+        <v>1.129607081178763</v>
       </c>
       <c r="T91">
-        <v>6.049491471094162</v>
+        <v>6.628429191066781</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.068347865775254</v>
+        <v>2.045366222822196</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1613969081178763</v>
+        <v>0.1610517781672107</v>
       </c>
       <c r="C92">
-        <v>0.5836590864977214</v>
+        <v>0.5722795169960722</v>
       </c>
       <c r="D92">
-        <v>1.943659086497721</v>
+        <v>1.949479516996072</v>
       </c>
       <c r="E92">
-        <v>1.548</v>
+        <v>1.5652</v>
       </c>
       <c r="F92">
-        <v>1.548</v>
+        <v>1.5652</v>
       </c>
       <c r="G92">
         <v>0.188</v>
@@ -8831,28 +8831,28 @@
         <v>0.24</v>
       </c>
       <c r="M92">
-        <v>0.1173384</v>
+        <v>0.11864216</v>
       </c>
       <c r="N92">
-        <v>0.1226616</v>
+        <v>0.12135784</v>
       </c>
       <c r="O92">
-        <v>0.03557186399999999</v>
+        <v>0.03519377359999999</v>
       </c>
       <c r="P92">
-        <v>0.08708973599999999</v>
+        <v>0.08616406639999999</v>
       </c>
       <c r="Q92">
-        <v>0.151089736</v>
+        <v>0.1501640664</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.129607081178763</v>
+        <v>1.245304424080119</v>
       </c>
       <c r="T92">
-        <v>6.628429191066781</v>
+        <v>7.336019737699982</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.045366222822196</v>
+        <v>2.022889670923051</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1610517781672107</v>
+        <v>0.1607066482165452</v>
       </c>
       <c r="C93">
-        <v>0.5722795169960722</v>
+        <v>0.5609349116139397</v>
       </c>
       <c r="D93">
-        <v>1.949479516996072</v>
+        <v>1.95533491161394</v>
       </c>
       <c r="E93">
-        <v>1.5652</v>
+        <v>1.5824</v>
       </c>
       <c r="F93">
-        <v>1.5652</v>
+        <v>1.5824</v>
       </c>
       <c r="G93">
         <v>0.188</v>
@@ -8913,28 +8913,28 @@
         <v>0.24</v>
       </c>
       <c r="M93">
-        <v>0.11864216</v>
+        <v>0.11994592</v>
       </c>
       <c r="N93">
-        <v>0.12135784</v>
+        <v>0.12005408</v>
       </c>
       <c r="O93">
-        <v>0.03519377359999999</v>
+        <v>0.03481568319999999</v>
       </c>
       <c r="P93">
-        <v>0.08616406639999999</v>
+        <v>0.08523839679999999</v>
       </c>
       <c r="Q93">
-        <v>0.1501640664</v>
+        <v>0.1492383968</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.245304424080119</v>
+        <v>1.389926102706815</v>
       </c>
       <c r="T93">
-        <v>7.336019737699982</v>
+        <v>8.220507920991484</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.022889670923051</v>
+        <v>2.000901739717365</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1607066482165452</v>
+        <v>0.1697377782658796</v>
       </c>
       <c r="C94">
-        <v>0.5609349116139397</v>
+        <v>0.4012530620611234</v>
       </c>
       <c r="D94">
-        <v>1.95533491161394</v>
+        <v>1.812853062061124</v>
       </c>
       <c r="E94">
-        <v>1.5824</v>
+        <v>1.5996</v>
       </c>
       <c r="F94">
-        <v>1.5824</v>
+        <v>1.5996</v>
       </c>
       <c r="G94">
         <v>0.188</v>
@@ -8995,45 +8995,45 @@
         <v>0.24</v>
       </c>
       <c r="M94">
-        <v>0.11994592</v>
+        <v>0.143964</v>
       </c>
       <c r="N94">
-        <v>0.12005408</v>
+        <v>0.09603599999999998</v>
       </c>
       <c r="O94">
-        <v>0.03481568319999999</v>
+        <v>0.02785043999999999</v>
       </c>
       <c r="P94">
-        <v>0.08523839679999999</v>
+        <v>0.06818555999999999</v>
       </c>
       <c r="Q94">
-        <v>0.1492383968</v>
+        <v>0.13218556</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.389926102706815</v>
+        <v>1.575868260941138</v>
       </c>
       <c r="T94">
-        <v>8.220507920991484</v>
+        <v>9.357707013794842</v>
       </c>
       <c r="U94">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V94">
         <v>0.29</v>
       </c>
       <c r="W94">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.000901739717365</v>
+        <v>1.667083437526048</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1697377782658796</v>
+        <v>0.1694934683152141</v>
       </c>
       <c r="C95">
-        <v>0.4012530620611234</v>
+        <v>0.3876336718393811</v>
       </c>
       <c r="D95">
-        <v>1.812853062061124</v>
+        <v>1.816433671839381</v>
       </c>
       <c r="E95">
-        <v>1.5996</v>
+        <v>1.6168</v>
       </c>
       <c r="F95">
-        <v>1.5996</v>
+        <v>1.6168</v>
       </c>
       <c r="G95">
         <v>0.188</v>
@@ -9077,28 +9077,28 @@
         <v>0.24</v>
       </c>
       <c r="M95">
-        <v>0.143964</v>
+        <v>0.145512</v>
       </c>
       <c r="N95">
-        <v>0.09603599999999998</v>
+        <v>0.09448799999999999</v>
       </c>
       <c r="O95">
-        <v>0.02785043999999999</v>
+        <v>0.02740152</v>
       </c>
       <c r="P95">
-        <v>0.06818555999999999</v>
+        <v>0.06708647999999999</v>
       </c>
       <c r="Q95">
-        <v>0.13218556</v>
+        <v>0.13108648</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.575868260941138</v>
+        <v>1.823791138586903</v>
       </c>
       <c r="T95">
-        <v>9.357707013794842</v>
+        <v>10.87397247086599</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.667083437526048</v>
+        <v>1.649348507339601</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1694934683152141</v>
+        <v>0.1692491583645485</v>
       </c>
       <c r="C96">
-        <v>0.3876336718393811</v>
+        <v>0.374028453907022</v>
       </c>
       <c r="D96">
-        <v>1.816433671839381</v>
+        <v>1.820028453907022</v>
       </c>
       <c r="E96">
-        <v>1.6168</v>
+        <v>1.634</v>
       </c>
       <c r="F96">
-        <v>1.6168</v>
+        <v>1.634</v>
       </c>
       <c r="G96">
         <v>0.188</v>
@@ -9159,28 +9159,28 @@
         <v>0.24</v>
       </c>
       <c r="M96">
-        <v>0.145512</v>
+        <v>0.14706</v>
       </c>
       <c r="N96">
-        <v>0.09448799999999999</v>
+        <v>0.09293999999999999</v>
       </c>
       <c r="O96">
-        <v>0.02740152</v>
+        <v>0.0269526</v>
       </c>
       <c r="P96">
-        <v>0.06708647999999999</v>
+        <v>0.0659874</v>
       </c>
       <c r="Q96">
-        <v>0.13108648</v>
+        <v>0.1299874</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.823791138586903</v>
+        <v>2.170883167290973</v>
       </c>
       <c r="T96">
-        <v>10.87397247086599</v>
+        <v>12.9967441107656</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.649348507339601</v>
+        <v>1.631986944104447</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1692491583645485</v>
+        <v>0.1690048484138829</v>
       </c>
       <c r="C97">
-        <v>0.374028453907022</v>
+        <v>0.3604374925731817</v>
       </c>
       <c r="D97">
-        <v>1.820028453907022</v>
+        <v>1.823637492573182</v>
       </c>
       <c r="E97">
-        <v>1.634</v>
+        <v>1.6512</v>
       </c>
       <c r="F97">
-        <v>1.634</v>
+        <v>1.6512</v>
       </c>
       <c r="G97">
         <v>0.188</v>
@@ -9241,28 +9241,28 @@
         <v>0.24</v>
       </c>
       <c r="M97">
-        <v>0.14706</v>
+        <v>0.148608</v>
       </c>
       <c r="N97">
-        <v>0.09293999999999999</v>
+        <v>0.091392</v>
       </c>
       <c r="O97">
-        <v>0.0269526</v>
+        <v>0.02650368</v>
       </c>
       <c r="P97">
-        <v>0.0659874</v>
+        <v>0.06488832</v>
       </c>
       <c r="Q97">
-        <v>0.1299874</v>
+        <v>0.12888832</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.170883167290973</v>
+        <v>2.691521210347079</v>
       </c>
       <c r="T97">
-        <v>12.9967441107656</v>
+        <v>16.18090157061501</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.631986944104447</v>
+        <v>1.614987080103359</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.169004848413883</v>
+        <v>0.1687605384632174</v>
       </c>
       <c r="C98">
-        <v>0.3604374925731813</v>
+        <v>0.3468608728170446</v>
       </c>
       <c r="D98">
-        <v>1.823637492573181</v>
+        <v>1.827260872817044</v>
       </c>
       <c r="E98">
-        <v>1.6512</v>
+        <v>1.6684</v>
       </c>
       <c r="F98">
-        <v>1.6512</v>
+        <v>1.6684</v>
       </c>
       <c r="G98">
         <v>0.188</v>
@@ -9323,28 +9323,28 @@
         <v>0.24</v>
       </c>
       <c r="M98">
-        <v>0.148608</v>
+        <v>0.150156</v>
       </c>
       <c r="N98">
-        <v>0.091392</v>
+        <v>0.08984400000000001</v>
       </c>
       <c r="O98">
-        <v>0.02650368</v>
+        <v>0.02605476</v>
       </c>
       <c r="P98">
-        <v>0.06488832</v>
+        <v>0.06378924000000001</v>
       </c>
       <c r="Q98">
-        <v>0.12888832</v>
+        <v>0.12778924</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.691521210347072</v>
+        <v>3.559251282107244</v>
       </c>
       <c r="T98">
-        <v>16.18090157061497</v>
+        <v>21.48783067036396</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.614987080103359</v>
+        <v>1.598337728762087</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1687605384632174</v>
+        <v>0.1685162285125519</v>
       </c>
       <c r="C99">
-        <v>0.3468608728170446</v>
+        <v>0.3332986802945235</v>
       </c>
       <c r="D99">
-        <v>1.827260872817044</v>
+        <v>1.830898680294524</v>
       </c>
       <c r="E99">
-        <v>1.6684</v>
+        <v>1.6856</v>
       </c>
       <c r="F99">
-        <v>1.6684</v>
+        <v>1.6856</v>
       </c>
       <c r="G99">
         <v>0.188</v>
@@ -9405,28 +9405,28 @@
         <v>0.24</v>
       </c>
       <c r="M99">
-        <v>0.150156</v>
+        <v>0.151704</v>
       </c>
       <c r="N99">
-        <v>0.08984400000000001</v>
+        <v>0.08829599999999999</v>
       </c>
       <c r="O99">
-        <v>0.02605476</v>
+        <v>0.02560583999999999</v>
       </c>
       <c r="P99">
-        <v>0.06378924000000001</v>
+        <v>0.06269015999999999</v>
       </c>
       <c r="Q99">
-        <v>0.12778924</v>
+        <v>0.12669016</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.559251282107244</v>
+        <v>5.29471142562759</v>
       </c>
       <c r="T99">
-        <v>21.48783067036396</v>
+        <v>32.10168886986196</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.598337728762087</v>
+        <v>1.58202816010125</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1685162285125519</v>
+        <v>0.1682719185618863</v>
       </c>
       <c r="C100">
-        <v>0.3332986802945235</v>
+        <v>0.3197510013450047</v>
       </c>
       <c r="D100">
-        <v>1.830898680294524</v>
+        <v>1.834551001345004</v>
       </c>
       <c r="E100">
-        <v>1.6856</v>
+        <v>1.7028</v>
       </c>
       <c r="F100">
-        <v>1.6856</v>
+        <v>1.7028</v>
       </c>
       <c r="G100">
         <v>0.188</v>
@@ -9487,28 +9487,28 @@
         <v>0.24</v>
       </c>
       <c r="M100">
-        <v>0.151704</v>
+        <v>0.153252</v>
       </c>
       <c r="N100">
-        <v>0.08829599999999999</v>
+        <v>0.08674800000000002</v>
       </c>
       <c r="O100">
-        <v>0.02560583999999999</v>
+        <v>0.02515692</v>
       </c>
       <c r="P100">
-        <v>0.06269015999999999</v>
+        <v>0.06159108000000002</v>
       </c>
       <c r="Q100">
-        <v>0.12669016</v>
+        <v>0.12559108</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.29471142562759</v>
+        <v>10.50109185618862</v>
       </c>
       <c r="T100">
-        <v>32.10168886986196</v>
+        <v>63.94326346835593</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.58202816010125</v>
+        <v>1.566048077675985</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1682719185618863</v>
-      </c>
-      <c r="C101">
-        <v>0.3197510013450047</v>
-      </c>
-      <c r="D101">
-        <v>1.834551001345004</v>
-      </c>
-      <c r="E101">
-        <v>1.7028</v>
-      </c>
-      <c r="F101">
-        <v>1.7028</v>
-      </c>
-      <c r="G101">
-        <v>0.188</v>
-      </c>
-      <c r="H101">
-        <v>1.72</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.304</v>
-      </c>
-      <c r="K101">
-        <v>0.064</v>
-      </c>
-      <c r="L101">
-        <v>0.24</v>
-      </c>
-      <c r="M101">
-        <v>0.153252</v>
-      </c>
-      <c r="N101">
-        <v>0.08674800000000002</v>
-      </c>
-      <c r="O101">
-        <v>0.02515692</v>
-      </c>
-      <c r="P101">
-        <v>0.06159108000000002</v>
-      </c>
-      <c r="Q101">
-        <v>0.12559108</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.50109185618862</v>
-      </c>
-      <c r="T101">
-        <v>63.94326346835593</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.29</v>
-      </c>
-      <c r="W101">
-        <v>0.0639</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.566048077675985</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
